--- a/outputs/54717.xlsx
+++ b/outputs/54717.xlsx
@@ -169,7 +169,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="210">
+  <fills count="154">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -178,230 +178,290 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5DBC8A"/>
-        <bgColor rgb="FF64BD88"/>
+        <fgColor rgb="FF61BD89"/>
+        <bgColor rgb="FF67BE87"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FF64BD88"/>
-        <bgColor rgb="FF5DBC8A"/>
+        <fgColor rgb="FF61BD89"/>
+        <bgColor rgb="FF67BE87"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67BE87"/>
+        <bgColor rgb="FF61BD89"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="mediumGray">
+        <fgColor rgb="FF67BE87"/>
+        <bgColor rgb="FF6DBF86"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FF64BD88"/>
-        <bgColor rgb="FF6ABE86"/>
+        <fgColor rgb="FF6DBF86"/>
+        <bgColor rgb="FF75C085"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6ABE86"/>
-        <bgColor rgb="FF72BF85"/>
+        <fgColor rgb="FF67BE87"/>
+        <bgColor rgb="FF6DBF86"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DBF86"/>
+        <bgColor rgb="FF67BE87"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FF72BF85"/>
-        <bgColor rgb="FF6ABE86"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FF64BD88"/>
-        <bgColor rgb="FF6ABE86"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FF6ABE86"/>
-        <bgColor rgb="FF72BF85"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF72BF85"/>
-        <bgColor rgb="FF77C084"/>
+        <fgColor rgb="FF75C085"/>
+        <bgColor rgb="FF6DBF86"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.15"/>
-        <bgColor rgb="FFD1CE71"/>
+        <bgColor rgb="FFD0CE72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="mediumGray">
+        <fgColor rgb="FF75C085"/>
+        <bgColor rgb="FF7AC183"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77C084"/>
-        <bgColor rgb="FF72BF85"/>
+        <fgColor rgb="FF7FC182"/>
+        <bgColor rgb="FF7AC183"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FF7FC182"/>
-        <bgColor rgb="FF8AC37F"/>
+        <fgColor rgb="FF8CC47F"/>
+        <bgColor rgb="FF7FC182"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="mediumGray">
+        <fgColor rgb="FF99C57D"/>
+        <bgColor rgb="FF93C57E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="mediumGray">
+        <fgColor rgb="FF99C57D"/>
+        <bgColor rgb="FF9EC77B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FF8AC37F"/>
+        <fgColor rgb="FF93C57E"/>
+        <bgColor rgb="FF8CC47F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FF7AC183"/>
         <bgColor rgb="FF7FC182"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF96C57D"/>
-        <bgColor rgb="FF99C57D"/>
+        <fgColor rgb="FF8CC47F"/>
+        <bgColor rgb="FF93C57E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA0C77B"/>
+        <bgColor rgb="FF9EC77B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5C87A"/>
+        <bgColor rgb="FFA8C878"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FF99C57D"/>
-        <bgColor rgb="FF9DC67B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91C47E"/>
-        <bgColor rgb="FF96C57D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FF77C084"/>
-        <bgColor rgb="FF7FC182"/>
+        <fgColor rgb="FFC1CC75"/>
+        <bgColor rgb="FFBBCB76"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FF8AC37F"/>
-        <bgColor rgb="FF91C47E"/>
+        <fgColor rgb="FFC5CD73"/>
+        <bgColor rgb="FFC1CC75"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFA1C77B"/>
-        <bgColor rgb="FF9DC67B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFA7C879"/>
-        <bgColor rgb="FFA1C77B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFC1CC74"/>
-        <bgColor rgb="FFBCCB75"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4CC73"/>
-        <bgColor rgb="FFC1CC74"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFCCCD72"/>
-        <bgColor rgb="FFC8CD72"/>
+        <fgColor rgb="FFCBCD72"/>
+        <bgColor rgb="FFC9CD72"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB0C978"/>
-        <bgColor rgb="FFABC878"/>
+        <bgColor rgb="FFAEC978"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5CD73"/>
+        <bgColor rgb="FFC9CD72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0D16D"/>
+        <bgColor rgb="FFDBD06E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5D16C"/>
+        <bgColor rgb="FFE0D16D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFC4CC73"/>
-        <bgColor rgb="FFC8CD72"/>
+        <fgColor rgb="FFEFD36B"/>
+        <bgColor rgb="FFEAD26B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBCB76"/>
+        <bgColor rgb="FFB7CA76"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFB7CA76"/>
+        <bgColor rgb="FFB3CA77"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBD06E"/>
+        <bgColor rgb="FFD6CF70"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFE0D16D"/>
+        <bgColor rgb="FFDBD06E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFD6CF70"/>
+        <bgColor rgb="FFD0CE72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFEAD26B"/>
+        <bgColor rgb="FFEFD36B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDCC67"/>
+        <bgColor rgb="FFFCCE67"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCC869"/>
+        <bgColor rgb="FFFDCC67"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAC269"/>
+        <bgColor rgb="FFF9BE6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFD0CE72"/>
+        <bgColor rgb="FFCBCD72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAD568"/>
+        <bgColor rgb="FFFDD567"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFFFD466"/>
+        <bgColor rgb="FFFED266"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6B26B"/>
+        <bgColor rgb="FFF7B56B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFF3A56E"/>
+        <bgColor rgb="FFF6AE6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFF19C6F"/>
+        <bgColor rgb="FFF3A56E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="mediumGray">
-        <fgColor rgb="FFDCD06E"/>
-        <bgColor rgb="FFE1D16D"/>
+        <fgColor rgb="FFF9BE6A"/>
+        <bgColor rgb="FFFAC269"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFE6D16C"/>
-        <bgColor rgb="FFE1D16D"/>
+        <fgColor rgb="FFF6B26B"/>
+        <bgColor rgb="FFF6AE6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8B71"/>
+        <bgColor rgb="FFEC9070"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFF0D36A"/>
-        <bgColor rgb="FFEBD26B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFB8CA76"/>
-        <bgColor rgb="FFBCCB75"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFB5CA77"/>
-        <bgColor rgb="FFB8CA76"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFD7CF6F"/>
-        <bgColor rgb="FFDCD06E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFE1D16D"/>
-        <bgColor rgb="FFDCD06E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFD7CF6F"/>
-        <bgColor rgb="FFD1CE71"/>
+        <fgColor rgb="FFE88072"/>
+        <bgColor rgb="FFEA8672"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEBD26B"/>
-        <bgColor rgb="FFE6D16C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFFCCB67"/>
-        <bgColor rgb="FFFDCF67"/>
+        <fgColor rgb="FFE88072"/>
+        <bgColor rgb="FFEA8672"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCC868"/>
-        <bgColor rgb="FFFCCB67"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFF9C069"/>
-        <bgColor rgb="FFFAC369"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFD1CE71"/>
-        <bgColor rgb="FFCCCD72"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9D568"/>
-        <bgColor rgb="FFFCD567"/>
+        <fgColor rgb="FFFDCF67"/>
+        <bgColor rgb="FFFCCE67"/>
       </patternFill>
     </fill>
     <fill>
@@ -411,1017 +471,621 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFF6B36B"/>
-        <bgColor rgb="FFF5AF6B"/>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC9070"/>
+        <bgColor rgb="FFEE9470"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFF2A46D"/>
-        <bgColor rgb="FFF4AC6C"/>
+        <fgColor rgb="FFF8BA6A"/>
+        <bgColor rgb="FFF7B56B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFF09D6E"/>
-        <bgColor rgb="FFF2A46D"/>
+        <fgColor rgb="FFEFD36B"/>
+        <bgColor rgb="FFF4D469"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9C069"/>
-        <bgColor rgb="FFFAC369"/>
+        <fgColor rgb="FFF6AE6B"/>
+        <bgColor rgb="FFF6B26B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFEC9070"/>
+        <bgColor rgb="FFEE9470"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8B71"/>
+        <bgColor rgb="FFEA8672"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="mediumGray">
-        <fgColor rgb="FFF5AF6B"/>
-        <bgColor rgb="FFF6B36B"/>
+        <fgColor rgb="FFEB8B71"/>
+        <bgColor rgb="FFEC9070"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFF4D469"/>
+        <bgColor rgb="FFEFD36B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="mediumGray">
-        <fgColor rgb="FFEA8871"/>
-        <bgColor rgb="FFEB8D70"/>
+        <fgColor rgb="FFFCC869"/>
+        <bgColor rgb="FFFDCC67"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9470"/>
+        <bgColor rgb="FFEC9070"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="mediumGray">
+        <fgColor rgb="FFEC9070"/>
+        <bgColor rgb="FFEE9470"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="mediumGray">
+        <fgColor rgb="FFF19C6F"/>
+        <bgColor rgb="FFEE9470"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFE98472"/>
-        <bgColor rgb="FFE77E72"/>
+        <fgColor rgb="FFFCC869"/>
+        <bgColor rgb="FFFAC269"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE77E72"/>
-        <bgColor rgb="FFE98472"/>
+        <fgColor rgb="FFEFD36B"/>
+        <bgColor rgb="FFEAD26B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDCF67"/>
+        <fgColor rgb="FFFED167"/>
         <bgColor rgb="FFFED266"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFFFD466"/>
-        <bgColor rgb="FFFED266"/>
+        <fgColor rgb="FFF7B56B"/>
+        <bgColor rgb="FFF8BA6A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFEC9170"/>
-        <bgColor rgb="FFEB8D70"/>
+        <fgColor rgb="FFF19C6F"/>
+        <bgColor rgb="FFEE9470"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFF8BB6A"/>
-        <bgColor rgb="FFF7B66A"/>
+        <fgColor rgb="FFEA8672"/>
+        <bgColor rgb="FFEB8B71"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFE0D16D"/>
+        <bgColor rgb="FFE5D16C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0D36A"/>
-        <bgColor rgb="FFEBD26B"/>
+        <fgColor rgb="FFF3A56E"/>
+        <bgColor rgb="FFF19C6F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4AC6C"/>
-        <bgColor rgb="FFF5AF6B"/>
+        <fgColor rgb="FFFDD567"/>
+        <bgColor rgb="FFFFD667"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFF3A56E"/>
+        <bgColor rgb="FFF19C6F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEC9170"/>
-        <bgColor rgb="FFEB8D70"/>
+        <fgColor rgb="FFFCCE67"/>
+        <bgColor rgb="FFFDCF67"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="mediumGray">
+        <fgColor rgb="FFFDD567"/>
+        <bgColor rgb="FFFFD667"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7B56B"/>
+        <bgColor rgb="FFF6B26B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFEA8871"/>
-        <bgColor rgb="FFEB8D70"/>
+        <fgColor rgb="FFF4D469"/>
+        <bgColor rgb="FFFAD568"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="mediumGray">
+        <fgColor rgb="FFF6B26B"/>
+        <bgColor rgb="FFF6AE6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFF6AE6B"/>
+        <bgColor rgb="FFF6B26B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFDBD06E"/>
+        <bgColor rgb="FFE0D16D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFFDCC67"/>
+        <bgColor rgb="FFFCCE67"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFFCCE67"/>
+        <bgColor rgb="FFFDCC67"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D70"/>
-        <bgColor rgb="FFEA8871"/>
+        <fgColor rgb="FFF8BA6A"/>
+        <bgColor rgb="FFF7B56B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFF0D36A"/>
-        <bgColor rgb="FFF5D469"/>
+        <fgColor rgb="FFF8BA6A"/>
+        <bgColor rgb="FFF9BE6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="mediumGray">
+        <fgColor rgb="FFFAD568"/>
+        <bgColor rgb="FFF4D469"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFFCCB67"/>
-        <bgColor rgb="FFFCC868"/>
+        <fgColor rgb="FFD0CE72"/>
+        <bgColor rgb="FFD6CF70"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFF7B66A"/>
-        <bgColor rgb="FFF8BB6A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFEE956F"/>
-        <bgColor rgb="FFEC9170"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFEC9170"/>
-        <bgColor rgb="FFEE956F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFEE956F"/>
-        <bgColor rgb="FFF09D6E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFFCC868"/>
-        <bgColor rgb="FFFAC369"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFEBD26B"/>
-        <bgColor rgb="FFF0D36A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFFED266"/>
-        <bgColor rgb="FFFDCF67"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7B66A"/>
-        <bgColor rgb="FFF6B36B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFF09D6E"/>
-        <bgColor rgb="FFEE956F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFEA8871"/>
-        <bgColor rgb="FFE98472"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1D16D"/>
-        <bgColor rgb="FFE6D16C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE956F"/>
-        <bgColor rgb="FFEC9170"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2A46D"/>
-        <bgColor rgb="FFF09D6E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFEB8D70"/>
-        <bgColor rgb="FFEA8871"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFE1D16D"/>
-        <bgColor rgb="FFE6D16C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFFED567"/>
-        <bgColor rgb="FFFCD567"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAC369"/>
-        <bgColor rgb="FFF9C069"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFF2A46D"/>
-        <bgColor rgb="FFF09D6E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFFDCF67"/>
-        <bgColor rgb="FFFCCB67"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1D16D"/>
-        <bgColor rgb="FFDCD06E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFED567"/>
-        <bgColor rgb="FFFFD466"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFF7B66A"/>
-        <bgColor rgb="FFF6B36B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF09D6E"/>
-        <bgColor rgb="FFF2A46D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFF5D469"/>
-        <bgColor rgb="FFF9D568"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFF5AF6B"/>
-        <bgColor rgb="FFF6B36B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5AF6B"/>
-        <bgColor rgb="FFF4AC6C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFF4AC6C"/>
-        <bgColor rgb="FFF2A46D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCD06E"/>
-        <bgColor rgb="FFE1D16D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCCB67"/>
-        <bgColor rgb="FFFCC868"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFFDCF67"/>
-        <bgColor rgb="FFFCCB67"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFF7B66A"/>
-        <bgColor rgb="FFF8BB6A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8BB6A"/>
-        <bgColor rgb="FFF7B66A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFF5D469"/>
-        <bgColor rgb="FFF9D568"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1CE71"/>
-        <bgColor rgb="FFCCCD72"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFEBD26B"/>
-        <bgColor rgb="FFF0D36A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFFDCF67"/>
+        <fgColor rgb="FFFED167"/>
         <bgColor rgb="FFFED266"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8BB6A"/>
-        <bgColor rgb="FFF9C069"/>
+        <fgColor rgb="FFF4D469"/>
+        <bgColor rgb="FFEFD36B"/>
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFF0D36A"/>
-        <bgColor rgb="FFF5D469"/>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFE5D16C"/>
+        <bgColor rgb="FFEAD26B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6D16C"/>
-        <bgColor rgb="FFEBD26B"/>
+        <fgColor rgb="FFF9BE6A"/>
+        <bgColor rgb="FFF8BA6A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFF9C069"/>
-        <bgColor rgb="FFF8BB6A"/>
+        <fgColor rgb="FFEA8672"/>
+        <bgColor rgb="FFE88072"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE98472"/>
-        <bgColor rgb="FFEA8871"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFF5D469"/>
-        <bgColor rgb="FFF0D36A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8CD72"/>
-        <bgColor rgb="FFCCCD72"/>
+        <fgColor rgb="FFC9CD72"/>
+        <bgColor rgb="FFCBCD72"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFD466"/>
-        <bgColor rgb="FFFED567"/>
+        <bgColor rgb="FFFDD567"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBCD72"/>
+        <bgColor rgb="FFC9CD72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1CC75"/>
+        <bgColor rgb="FFC5CD73"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0CE72"/>
+        <bgColor rgb="FFCBCD72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="mediumGray">
+        <fgColor rgb="FFFAD568"/>
+        <bgColor rgb="FFFDD567"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFFAC369"/>
-        <bgColor rgb="FFF9C069"/>
+        <fgColor rgb="FFEC9070"/>
+        <bgColor rgb="FFEB8B71"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFD6CF70"/>
+        <bgColor rgb="FFDBD06E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFBBCB76"/>
+        <bgColor rgb="FFB7CA76"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D70"/>
-        <bgColor rgb="FFEC9170"/>
+        <fgColor rgb="FFEAD26B"/>
+        <bgColor rgb="FFE5D16C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFFAD568"/>
+        <bgColor rgb="FFF4D469"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3CA77"/>
+        <bgColor rgb="FFB0C978"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEC978"/>
+        <bgColor rgb="FFABC878"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFF9BE6A"/>
+        <bgColor rgb="FFF8BA6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFB3CA77"/>
+        <bgColor rgb="FFB0C978"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7CA76"/>
+        <bgColor rgb="FFB3CA77"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7CA76"/>
+        <bgColor rgb="FFB3CA77"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8C878"/>
+        <bgColor rgb="FFABC878"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFB7CA76"/>
+        <bgColor rgb="FFBBCB76"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="mediumGray">
-        <fgColor rgb="FFE98472"/>
-        <bgColor rgb="FFE77E72"/>
+        <fgColor rgb="FFC1CC75"/>
+        <bgColor rgb="FFC5CD73"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="mediumGray">
+        <fgColor rgb="FFC1CC75"/>
+        <bgColor rgb="FFBBCB76"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6D16C"/>
-        <bgColor rgb="FFE1D16D"/>
+        <fgColor rgb="FF99C57D"/>
+        <bgColor rgb="FF93C57E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCCD72"/>
-        <bgColor rgb="FFC8CD72"/>
+        <fgColor rgb="FFFFD667"/>
+        <bgColor rgb="FFFDD567"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5D469"/>
-        <bgColor rgb="FFF0D36A"/>
+        <fgColor rgb="FFF9BE6A"/>
+        <bgColor rgb="FFFAC269"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9EC77B"/>
+        <bgColor rgb="FFA0C77B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFBBCB76"/>
+        <bgColor rgb="FFC1CC75"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFED266"/>
+        <bgColor rgb="FFFED167"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEC978"/>
+        <bgColor rgb="FFB0C978"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FF8CC47F"/>
+        <bgColor rgb="FF93C57E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="mediumGray">
-        <fgColor rgb="FFFAC369"/>
-        <bgColor rgb="FFFCC868"/>
+        <fgColor rgb="FFBBCB76"/>
+        <bgColor rgb="FFB7CA76"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="mediumGray">
+        <fgColor rgb="FF8CC47F"/>
+        <bgColor rgb="FF93C57E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="mediumGray">
+        <fgColor rgb="FF9EC77B"/>
+        <bgColor rgb="FFA0C77B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="mediumGray">
+        <fgColor rgb="FFA8C878"/>
+        <bgColor rgb="FFABC878"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC1CC74"/>
-        <bgColor rgb="FFC4CC73"/>
+        <fgColor rgb="FF9EC77B"/>
+        <bgColor rgb="FFA0C77B"/>
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFCCCD72"/>
-        <bgColor rgb="FFD1CE71"/>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC183"/>
+        <bgColor rgb="FF75C085"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFFCD567"/>
-        <bgColor rgb="FFF9D568"/>
+        <fgColor rgb="FFEAD26B"/>
+        <bgColor rgb="FFE5D16C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABC878"/>
+        <bgColor rgb="FFA8C878"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99C57D"/>
+        <bgColor rgb="FF9EC77B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3CA77"/>
+        <bgColor rgb="FFB0C978"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FC182"/>
+        <bgColor rgb="FF7AC183"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5D16C"/>
+        <bgColor rgb="FFE0D16D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFEB8D70"/>
-        <bgColor rgb="FFEC9170"/>
+        <fgColor rgb="FFEFD36B"/>
+        <bgColor rgb="FFEAD26B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFCCCD72"/>
-        <bgColor rgb="FFC8CD72"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7CF6F"/>
-        <bgColor rgb="FFDCD06E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFBCCB75"/>
-        <bgColor rgb="FFB8CA76"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFE6D16C"/>
-        <bgColor rgb="FFEBD26B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFF9D568"/>
-        <bgColor rgb="FFFCD567"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFF4AC6C"/>
-        <bgColor rgb="FFF5AF6B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFD7CF6F"/>
-        <bgColor rgb="FFD1CE71"/>
+        <fgColor rgb="FFF4D469"/>
+        <bgColor rgb="FFFAD568"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFF9D568"/>
-        <bgColor rgb="FFF5D469"/>
+        <fgColor rgb="FF99C57D"/>
+        <bgColor rgb="FF9EC77B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFB0C978"/>
-        <bgColor rgb="FFB5CA77"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7CF6F"/>
-        <bgColor rgb="FFD1CE71"/>
+        <fgColor rgb="FFEAD26B"/>
+        <bgColor rgb="FFE5D16C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
         <fgColor rgb="FFABC878"/>
-        <bgColor rgb="FFB0C978"/>
+        <bgColor rgb="FFA8C878"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFDCD06E"/>
-        <bgColor rgb="FFE1D16D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFF8BB6A"/>
-        <bgColor rgb="FFF9C069"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFF5AF6B"/>
-        <bgColor rgb="FFF4AC6C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFC8CD72"/>
-        <bgColor rgb="FFCCCD72"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFBCCB75"/>
-        <bgColor rgb="FFC1CC74"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFB5CA77"/>
-        <bgColor rgb="FFB0C978"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8CD72"/>
-        <bgColor rgb="FFC4CC73"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1C77B"/>
-        <bgColor rgb="FF9DC67B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFB8CA76"/>
-        <bgColor rgb="FFB5CA77"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCD06E"/>
-        <bgColor rgb="FFD7CF6F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFB5CA77"/>
-        <bgColor rgb="FFB8CA76"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFA7C879"/>
-        <bgColor rgb="FFABC878"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFA7C879"/>
-        <bgColor rgb="FFA1C77B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8CA76"/>
-        <bgColor rgb="FFB5CA77"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFA1C77B"/>
-        <bgColor rgb="FFA7C879"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFB0C978"/>
-        <bgColor rgb="FFB5CA77"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFC4CC73"/>
-        <bgColor rgb="FFC1CC74"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0C978"/>
-        <bgColor rgb="FFB5CA77"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFBCCB75"/>
-        <bgColor rgb="FFC1CC74"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FF96C57D"/>
-        <bgColor rgb="FF99C57D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFD666"/>
-        <bgColor rgb="FFFED567"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFF8BB6A"/>
-        <bgColor rgb="FFF9C069"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DC67B"/>
-        <bgColor rgb="FFA1C77B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBCCB75"/>
-        <bgColor rgb="FFB8CA76"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFED266"/>
-        <bgColor rgb="FFFFD466"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFB0C978"/>
-        <bgColor rgb="FFABC878"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FF8AC37F"/>
-        <bgColor rgb="FF91C47E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FF9DC67B"/>
-        <bgColor rgb="FFA1C77B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFB8CA76"/>
-        <bgColor rgb="FFBCCB75"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FF91C47E"/>
-        <bgColor rgb="FF8AC37F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FF9DC67B"/>
-        <bgColor rgb="FFA1C77B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0D36A"/>
-        <bgColor rgb="FFF5D469"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFA7C879"/>
-        <bgColor rgb="FFABC878"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FF99C57D"/>
-        <bgColor rgb="FF96C57D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBCCB75"/>
-        <bgColor rgb="FFB8CA76"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FF77C084"/>
-        <bgColor rgb="FF7FC182"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8AC37F"/>
-        <bgColor rgb="FF91C47E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFEBD26B"/>
-        <bgColor rgb="FFE6D16C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABC878"/>
-        <bgColor rgb="FFA7C879"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96C57D"/>
-        <bgColor rgb="FF99C57D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99C57D"/>
-        <bgColor rgb="FF96C57D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FF7FC182"/>
-        <bgColor rgb="FF77C084"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FC182"/>
-        <bgColor rgb="FF77C084"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9D568"/>
-        <bgColor rgb="FFF5D469"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFEBD26B"/>
-        <bgColor rgb="FFF0D36A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FF9DC67B"/>
-        <bgColor rgb="FF99C57D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6ABE86"/>
-        <bgColor rgb="FF64BD88"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFE6D16C"/>
-        <bgColor rgb="FFEBD26B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FF99C57D"/>
-        <bgColor rgb="FF96C57D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFABC878"/>
-        <bgColor rgb="FFA7C879"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FF96C57D"/>
-        <bgColor rgb="FF91C47E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DC67B"/>
+        <fgColor rgb="FF93C57E"/>
         <bgColor rgb="FF99C57D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FFDCD06E"/>
-        <bgColor rgb="FFD7CF6F"/>
+        <fgColor rgb="FFDBD06E"/>
+        <bgColor rgb="FFD6CF70"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93C57E"/>
+        <bgColor rgb="FF99C57D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="mediumGray">
-        <fgColor rgb="FF5DBC8A"/>
-        <bgColor rgb="FF64BD88"/>
+        <fgColor rgb="FFFDCC67"/>
+        <bgColor rgb="FFFCC869"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
-        <fgColor rgb="FF5DBC8A"/>
-        <bgColor rgb="FF64BD88"/>
+        <fgColor rgb="FFA8C878"/>
+        <bgColor rgb="FFA5C87A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="mediumGray">
-        <fgColor rgb="FF6ABE86"/>
-        <bgColor rgb="FF72BF85"/>
+        <fgColor rgb="FF61BD89"/>
+        <bgColor rgb="FF67BE87"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FF67BE87"/>
+        <bgColor rgb="FF6DBF86"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFFDD567"/>
+        <bgColor rgb="FFFAD568"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5D469"/>
-        <bgColor rgb="FFF9D568"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FF91C47E"/>
-        <bgColor rgb="FF96C57D"/>
+        <fgColor rgb="FF75C085"/>
+        <bgColor rgb="FF7AC183"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="mediumGray">
-        <fgColor rgb="FFFCC868"/>
-        <bgColor rgb="FFFCCB67"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7C879"/>
-        <bgColor rgb="FFABC878"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BD88"/>
-        <bgColor rgb="FF6ABE86"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FF6ABE86"/>
-        <bgColor rgb="FF64BD88"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCD567"/>
-        <bgColor rgb="FFFED567"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FF72BF85"/>
-        <bgColor rgb="FF77C084"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFCCCD72"/>
-        <bgColor rgb="FFD1CE71"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FF72BF85"/>
-        <bgColor rgb="FF77C084"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFD7CF6F"/>
-        <bgColor rgb="FFDCD06E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FF77C084"/>
-        <bgColor rgb="FF72BF85"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFD1CE71"/>
-        <bgColor rgb="FFD7CF6F"/>
+        <fgColor rgb="FFD6CF70"/>
+        <bgColor rgb="FFD0CE72"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="darkGray">
         <fgColor rgb="FF7FC182"/>
-        <bgColor rgb="FF77C084"/>
+        <bgColor rgb="FF7AC183"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="mediumGray">
-        <fgColor rgb="FFF6B36B"/>
-        <bgColor rgb="FFF7B66A"/>
+        <fgColor rgb="FFF6B26B"/>
+        <bgColor rgb="FFF7B56B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFA5C87A"/>
+        <bgColor rgb="FFA0C77B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="darkGray">
+        <fgColor rgb="FFEE9470"/>
+        <bgColor rgb="FFEC9070"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6B36B"/>
-        <bgColor rgb="FFF7B66A"/>
+        <fgColor rgb="FFEA8672"/>
+        <bgColor rgb="FFE88072"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8672"/>
+        <bgColor rgb="FFEB8B71"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="mediumGray">
-        <fgColor rgb="FFC1CC74"/>
-        <bgColor rgb="FFC4CC73"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFBCCB75"/>
-        <bgColor rgb="FFC1CC74"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFA1C77B"/>
-        <bgColor rgb="FFA7C879"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFEE956F"/>
-        <bgColor rgb="FFEC9170"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFE98472"/>
-        <bgColor rgb="FFEA8871"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFABC878"/>
-        <bgColor rgb="FFB0C978"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkGray">
-        <fgColor rgb="FFE77E72"/>
-        <bgColor rgb="FFE98472"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFF09D6E"/>
-        <bgColor rgb="FFF2A46D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor rgb="FFE98472"/>
-        <bgColor rgb="FFEA8871"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8871"/>
-        <bgColor rgb="FFE98472"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2A46D"/>
-        <bgColor rgb="FFF4AC6C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77E72"/>
-        <bgColor rgb="FFE98472"/>
+        <fgColor rgb="FFEA8672"/>
+        <bgColor rgb="FFEB8B71"/>
       </patternFill>
     </fill>
   </fills>
@@ -1435,42 +1099,42 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </left>
       <right style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </right>
       <top style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </top>
       <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </left>
       <right style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </right>
       <top style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </left>
       <right/>
       <top style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </top>
       <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1484,63 +1148,63 @@
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </right>
       <top style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </top>
       <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </left>
       <right style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </left>
       <right style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </right>
       <top style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </top>
       <bottom style="medium"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </left>
       <right style="medium"/>
       <top style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </top>
       <bottom style="medium"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </left>
       <right style="medium"/>
       <top style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </top>
       <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFCDCDCD"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1570,984 +1234,764 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="190">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="18" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="18" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="20" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="20" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="27" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="27" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="28" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="28" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="29" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="29" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="32" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="32" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="34" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="34" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="35" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="35" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="36" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="36" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="37" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="37" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="38" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="38" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="39" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="39" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="40" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="40" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="41" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="41" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="42" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="42" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="43" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="43" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="44" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="44" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="45" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="45" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="46" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="46" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="47" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="47" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="48" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="48" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="49" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="49" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="50" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="50" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="51" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="51" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="52" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="52" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="53" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="53" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="54" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="54" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="55" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="55" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="56" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="56" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="57" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="57" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="58" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="58" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="59" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="59" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="60" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="60" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="61" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="61" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="62" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="62" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="63" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="63" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="64" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="64" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="65" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="65" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="66" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="66" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="67" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="67" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="68" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="68" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="69" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="69" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="70" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="70" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="71" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="71" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="72" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="72" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="73" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="73" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="74" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="74" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="75" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="75" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="76" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="76" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="77" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="77" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="78" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="78" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="79" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="79" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="80" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="80" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="81" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="81" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="82" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="82" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="83" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="83" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="84" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="84" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="85" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="85" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="86" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="86" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="87" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="87" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="88" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="88" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="89" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="89" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="90" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="90" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="91" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="91" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="92" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="92" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="93" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="93" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="94" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="94" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="95" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="95" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="96" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="96" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="97" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="97" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="98" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="98" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="99" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="99" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="100" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="100" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="101" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="101" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="102" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="102" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="103" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="103" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="104" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="104" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="105" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="105" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="106" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="23" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="107" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="106" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="108" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="107" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="109" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="106" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="110" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="108" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="111" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="91" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="112" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="113" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="109" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="114" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="109" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="115" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="110" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="116" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="111" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="117" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="112" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="118" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="113" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="119" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="114" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="120" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="115" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="121" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="116" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="122" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="38" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="123" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="105" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="124" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="117" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="125" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="118" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="126" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="119" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="127" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="120" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="128" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="121" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="129" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="122" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="130" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="123" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="131" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="112" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="23" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="124" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="132" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="116" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="133" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="125" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="134" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="126" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="135" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="49" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="136" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="127" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="134" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="137" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="128" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="102" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="129" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="138" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="120" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="139" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="130" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="139" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="131" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="140" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="39" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="141" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="117" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="142" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="117" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="143" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="108" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="144" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="128" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="145" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="24" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="146" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="132" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="147" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="133" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="148" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="71" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="149" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="38" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="134" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="131" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="85" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="150" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="151" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="135" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="152" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="74" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="153" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="136" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="154" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="127" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="155" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="137" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="156" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="138" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="157" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="139" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="158" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="140" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="159" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="141" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="153" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="142" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="160" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="143" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="161" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="144" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="162" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="145" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="163" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="146" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="49" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="147" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="164" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="148" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="165" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="111" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="166" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="149" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="141" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="150" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="154" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="151" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="167" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="152" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="168" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="153" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="168" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="48" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="74" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="169" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="150" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="150" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="137" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="166" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="143" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="170" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="109" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="75" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="171" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="93" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="172" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="173" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="80" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="174" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="175" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="164" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="176" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="177" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="178" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="179" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="180" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="181" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="182" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="183" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="136" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="184" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="185" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="186" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="187" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="188" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="189" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="190" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="191" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="192" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="193" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="194" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="195" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="196" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="197" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="198" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="199" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="200" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="201" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="202" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="203" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="204" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="205" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="206" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="207" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="208" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="209" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2563,61 +2007,61 @@
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFF5D469"/>
-      <rgbColor rgb="FFF4AC6C"/>
+      <rgbColor rgb="FFF4D469"/>
+      <rgbColor rgb="FFF6B26B"/>
       <rgbColor rgb="FFABC878"/>
       <rgbColor rgb="FFFDCF67"/>
-      <rgbColor rgb="FFFED567"/>
-      <rgbColor rgb="FFF5AF6B"/>
+      <rgbColor rgb="FFFDD567"/>
+      <rgbColor rgb="FFF7B56B"/>
+      <rgbColor rgb="FFAEC978"/>
+      <rgbColor rgb="FFE0D16D"/>
+      <rgbColor rgb="FFB3CA77"/>
+      <rgbColor rgb="FFFDCC67"/>
+      <rgbColor rgb="FF75C085"/>
+      <rgbColor rgb="FFF9BE6A"/>
+      <rgbColor rgb="FF9EC77B"/>
+      <rgbColor rgb="FFCDCDCD"/>
+      <rgbColor rgb="FF6DBF86"/>
+      <rgbColor rgb="FF7AC183"/>
+      <rgbColor rgb="FFEB8B71"/>
+      <rgbColor rgb="FFFAD568"/>
+      <rgbColor rgb="FFD6CF70"/>
+      <rgbColor rgb="FFEAD26B"/>
+      <rgbColor rgb="FFEA8672"/>
+      <rgbColor rgb="FFB7CA76"/>
+      <rgbColor rgb="FFC1CC75"/>
+      <rgbColor rgb="FFFCCE67"/>
+      <rgbColor rgb="FFF8BA6A"/>
+      <rgbColor rgb="FFFFD466"/>
       <rgbColor rgb="FFB0C978"/>
-      <rgbColor rgb="FFFAC369"/>
-      <rgbColor rgb="FFB8CA76"/>
-      <rgbColor rgb="FFFCCB67"/>
-      <rgbColor rgb="FF6ABE86"/>
-      <rgbColor rgb="FFF8BB6A"/>
+      <rgbColor rgb="FFFAC269"/>
+      <rgbColor rgb="FFE5D16C"/>
+      <rgbColor rgb="FFA0C77B"/>
+      <rgbColor rgb="FFFED167"/>
       <rgbColor rgb="FF99C57D"/>
-      <rgbColor rgb="FFCCCCCC"/>
-      <rgbColor rgb="FF72BF85"/>
-      <rgbColor rgb="FF77C084"/>
-      <rgbColor rgb="FFEA8871"/>
-      <rgbColor rgb="FFF9D568"/>
-      <rgbColor rgb="FFCCCD72"/>
-      <rgbColor rgb="FFE6D16C"/>
-      <rgbColor rgb="FFE98472"/>
-      <rgbColor rgb="FFBCCB75"/>
-      <rgbColor rgb="FFC1CC74"/>
-      <rgbColor rgb="FFF0D36A"/>
-      <rgbColor rgb="FFF6B36B"/>
-      <rgbColor rgb="FFFCD567"/>
-      <rgbColor rgb="FFB5CA77"/>
-      <rgbColor rgb="FFF9C069"/>
-      <rgbColor rgb="FFE1D16D"/>
-      <rgbColor rgb="FF9DC67B"/>
-      <rgbColor rgb="FFFFD466"/>
-      <rgbColor rgb="FF96C57D"/>
-      <rgbColor rgb="FFC8CD72"/>
-      <rgbColor rgb="FFD1CE71"/>
-      <rgbColor rgb="FFFFD666"/>
-      <rgbColor rgb="FF91C47E"/>
-      <rgbColor rgb="FFEE956F"/>
-      <rgbColor rgb="FFEC9170"/>
-      <rgbColor rgb="FFFCC868"/>
-      <rgbColor rgb="FFA1C77B"/>
-      <rgbColor rgb="FF5DBC8A"/>
-      <rgbColor rgb="FFA7C879"/>
+      <rgbColor rgb="FFC5CD73"/>
+      <rgbColor rgb="FFD0CE72"/>
+      <rgbColor rgb="FFFFD667"/>
+      <rgbColor rgb="FF93C57E"/>
+      <rgbColor rgb="FFF19C6F"/>
+      <rgbColor rgb="FFEC9070"/>
+      <rgbColor rgb="FFFCC869"/>
+      <rgbColor rgb="FFA5C87A"/>
+      <rgbColor rgb="FF61BD89"/>
+      <rgbColor rgb="FFA8C878"/>
       <rgbColor rgb="FFFED266"/>
-      <rgbColor rgb="FFF09D6E"/>
-      <rgbColor rgb="FFE77E72"/>
-      <rgbColor rgb="FF8AC37F"/>
+      <rgbColor rgb="FFF3A56E"/>
+      <rgbColor rgb="FFE88072"/>
+      <rgbColor rgb="FF8CC47F"/>
       <rgbColor rgb="FF7FC182"/>
-      <rgbColor rgb="FFDCD06E"/>
-      <rgbColor rgb="FF64BD88"/>
-      <rgbColor rgb="FFEBD26B"/>
-      <rgbColor rgb="FFD7CF6F"/>
-      <rgbColor rgb="FFF2A46D"/>
-      <rgbColor rgb="FFEB8D70"/>
-      <rgbColor rgb="FFC4CC73"/>
-      <rgbColor rgb="FFF7B66A"/>
+      <rgbColor rgb="FFDBD06E"/>
+      <rgbColor rgb="FF67BE87"/>
+      <rgbColor rgb="FFEFD36B"/>
+      <rgbColor rgb="FFCBCD72"/>
+      <rgbColor rgb="FFF6AE6B"/>
+      <rgbColor rgb="FFEE9470"/>
+      <rgbColor rgb="FFBBCB76"/>
+      <rgbColor rgb="FFC9CD72"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -3449,7 +2893,7 @@
         <v>29</v>
       </c>
       <c r="S10" s="1" t="n">
-        <f aca="true">SUM(OFFSET($B$3,S6-1,MATCH(S4,$B$2:$P$2,0)-1,S8-S6+1,1))</f>
+        <f aca="false">SUM(INDEX(B:P,S6+2,MATCH(S4,B2:P2,0)):INDEX(B:P,S8+2,MATCH(S4,B2:P2,0)))</f>
         <v>4304</v>
       </c>
       <c r="T10" s="1"/>
@@ -3611,22 +3055,22 @@
       <c r="D13" s="64" t="n">
         <v>386</v>
       </c>
-      <c r="E13" s="65" t="n">
+      <c r="E13" s="57" t="n">
         <v>438</v>
       </c>
       <c r="F13" s="46" t="n">
         <v>451</v>
       </c>
-      <c r="G13" s="66" t="n">
+      <c r="G13" s="65" t="n">
         <v>536</v>
       </c>
-      <c r="H13" s="66" t="n">
+      <c r="H13" s="65" t="n">
         <v>536</v>
       </c>
-      <c r="I13" s="67" t="n">
+      <c r="I13" s="66" t="n">
         <v>540</v>
       </c>
-      <c r="J13" s="68" t="n">
+      <c r="J13" s="67" t="n">
         <v>521</v>
       </c>
       <c r="K13" s="53" t="n">
@@ -3668,37 +3112,37 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="69" t="n">
+      <c r="B14" s="68" t="n">
         <v>396</v>
       </c>
-      <c r="C14" s="70" t="n">
+      <c r="C14" s="69" t="n">
         <v>316</v>
       </c>
-      <c r="D14" s="71" t="n">
+      <c r="D14" s="70" t="n">
         <v>364</v>
       </c>
       <c r="E14" s="49" t="n">
         <v>416</v>
       </c>
-      <c r="F14" s="72" t="n">
+      <c r="F14" s="71" t="n">
         <v>440</v>
       </c>
-      <c r="G14" s="68" t="n">
+      <c r="G14" s="67" t="n">
         <v>520</v>
       </c>
-      <c r="H14" s="68" t="n">
+      <c r="H14" s="67" t="n">
         <v>520</v>
       </c>
-      <c r="I14" s="66" t="n">
+      <c r="I14" s="65" t="n">
         <v>535</v>
       </c>
-      <c r="J14" s="73" t="n">
+      <c r="J14" s="72" t="n">
         <v>515</v>
       </c>
-      <c r="K14" s="74" t="n">
+      <c r="K14" s="73" t="n">
         <v>572</v>
       </c>
-      <c r="L14" s="74" t="n">
+      <c r="L14" s="73" t="n">
         <v>572</v>
       </c>
       <c r="M14" s="53" t="n">
@@ -3737,7 +3181,7 @@
       <c r="B15" s="64" t="n">
         <v>385</v>
       </c>
-      <c r="C15" s="75" t="n">
+      <c r="C15" s="74" t="n">
         <v>292</v>
       </c>
       <c r="D15" s="45" t="n">
@@ -3755,16 +3199,16 @@
       <c r="H15" s="48" t="n">
         <v>504</v>
       </c>
-      <c r="I15" s="76" t="n">
+      <c r="I15" s="65" t="n">
         <v>529</v>
       </c>
-      <c r="J15" s="77" t="n">
+      <c r="J15" s="75" t="n">
         <v>491</v>
       </c>
-      <c r="K15" s="78" t="n">
+      <c r="K15" s="61" t="n">
         <v>559</v>
       </c>
-      <c r="L15" s="78" t="n">
+      <c r="L15" s="61" t="n">
         <v>559</v>
       </c>
       <c r="M15" s="53" t="n">
@@ -3800,37 +3244,37 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="69" t="n">
+      <c r="B16" s="68" t="n">
         <v>394</v>
       </c>
-      <c r="C16" s="79" t="n">
+      <c r="C16" s="31" t="n">
         <v>296</v>
       </c>
-      <c r="D16" s="80" t="n">
+      <c r="D16" s="76" t="n">
         <v>348</v>
       </c>
-      <c r="E16" s="81" t="n">
+      <c r="E16" s="42" t="n">
         <v>403</v>
       </c>
       <c r="F16" s="42" t="n">
         <v>411</v>
       </c>
-      <c r="G16" s="82" t="n">
+      <c r="G16" s="77" t="n">
         <v>498</v>
       </c>
-      <c r="H16" s="82" t="n">
+      <c r="H16" s="77" t="n">
         <v>498</v>
       </c>
-      <c r="I16" s="82" t="n">
+      <c r="I16" s="77" t="n">
         <v>495</v>
       </c>
       <c r="J16" s="47" t="n">
         <v>486</v>
       </c>
-      <c r="K16" s="73" t="n">
+      <c r="K16" s="72" t="n">
         <v>519</v>
       </c>
-      <c r="L16" s="73" t="n">
+      <c r="L16" s="72" t="n">
         <v>519</v>
       </c>
       <c r="M16" s="53" t="n">
@@ -3866,19 +3310,19 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="83" t="n">
+      <c r="B17" s="78" t="n">
         <v>374</v>
       </c>
-      <c r="C17" s="84" t="n">
+      <c r="C17" s="74" t="n">
         <v>291</v>
       </c>
-      <c r="D17" s="85" t="n">
+      <c r="D17" s="79" t="n">
         <v>355</v>
       </c>
       <c r="E17" s="49" t="n">
         <v>412</v>
       </c>
-      <c r="F17" s="81" t="n">
+      <c r="F17" s="42" t="n">
         <v>402</v>
       </c>
       <c r="G17" s="47" t="n">
@@ -3887,16 +3331,16 @@
       <c r="H17" s="47" t="n">
         <v>483</v>
       </c>
-      <c r="I17" s="77" t="n">
+      <c r="I17" s="75" t="n">
         <v>491</v>
       </c>
-      <c r="J17" s="86" t="n">
+      <c r="J17" s="80" t="n">
         <v>444</v>
       </c>
-      <c r="K17" s="87" t="n">
+      <c r="K17" s="48" t="n">
         <v>509</v>
       </c>
-      <c r="L17" s="87" t="n">
+      <c r="L17" s="48" t="n">
         <v>509</v>
       </c>
       <c r="M17" s="53" t="n">
@@ -3932,37 +3376,37 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="71" t="n">
+      <c r="B18" s="70" t="n">
         <v>364</v>
       </c>
       <c r="C18" s="36" t="n">
         <v>277</v>
       </c>
-      <c r="D18" s="88" t="n">
+      <c r="D18" s="81" t="n">
         <v>334</v>
       </c>
-      <c r="E18" s="69" t="n">
+      <c r="E18" s="68" t="n">
         <v>392</v>
       </c>
-      <c r="F18" s="81" t="n">
+      <c r="F18" s="42" t="n">
         <v>402</v>
       </c>
-      <c r="G18" s="89" t="n">
+      <c r="G18" s="82" t="n">
         <v>458</v>
       </c>
-      <c r="H18" s="89" t="n">
+      <c r="H18" s="82" t="n">
         <v>458</v>
       </c>
-      <c r="I18" s="90" t="n">
+      <c r="I18" s="83" t="n">
         <v>460</v>
       </c>
       <c r="J18" s="57" t="n">
         <v>432</v>
       </c>
-      <c r="K18" s="91" t="n">
+      <c r="K18" s="47" t="n">
         <v>478</v>
       </c>
-      <c r="L18" s="91" t="n">
+      <c r="L18" s="47" t="n">
         <v>478</v>
       </c>
       <c r="M18" s="53" t="n">
@@ -3998,31 +3442,31 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="85" t="n">
+      <c r="B19" s="79" t="n">
         <v>354</v>
       </c>
-      <c r="C19" s="92" t="n">
+      <c r="C19" s="84" t="n">
         <v>283</v>
       </c>
       <c r="D19" s="63" t="n">
         <v>324</v>
       </c>
-      <c r="E19" s="93" t="n">
+      <c r="E19" s="85" t="n">
         <v>383</v>
       </c>
-      <c r="F19" s="94" t="n">
+      <c r="F19" s="86" t="n">
         <v>376</v>
       </c>
-      <c r="G19" s="95" t="n">
+      <c r="G19" s="87" t="n">
         <v>435</v>
       </c>
-      <c r="H19" s="95" t="n">
+      <c r="H19" s="87" t="n">
         <v>435</v>
       </c>
-      <c r="I19" s="65" t="n">
+      <c r="I19" s="57" t="n">
         <v>438</v>
       </c>
-      <c r="J19" s="96" t="n">
+      <c r="J19" s="88" t="n">
         <v>429</v>
       </c>
       <c r="K19" s="59" t="n">
@@ -4064,19 +3508,19 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="97" t="n">
+      <c r="B20" s="89" t="n">
         <v>335</v>
       </c>
-      <c r="C20" s="98" t="n">
+      <c r="C20" s="90" t="n">
         <v>260</v>
       </c>
-      <c r="D20" s="99" t="n">
+      <c r="D20" s="32" t="n">
         <v>313</v>
       </c>
-      <c r="E20" s="83" t="n">
+      <c r="E20" s="78" t="n">
         <v>373</v>
       </c>
-      <c r="F20" s="100" t="n">
+      <c r="F20" s="91" t="n">
         <v>367</v>
       </c>
       <c r="G20" s="57" t="n">
@@ -4085,16 +3529,16 @@
       <c r="H20" s="57" t="n">
         <v>432</v>
       </c>
-      <c r="I20" s="101" t="n">
+      <c r="I20" s="88" t="n">
         <v>426</v>
       </c>
-      <c r="J20" s="69" t="n">
+      <c r="J20" s="68" t="n">
         <v>397</v>
       </c>
-      <c r="K20" s="72" t="n">
+      <c r="K20" s="71" t="n">
         <v>440</v>
       </c>
-      <c r="L20" s="72" t="n">
+      <c r="L20" s="71" t="n">
         <v>440</v>
       </c>
       <c r="M20" s="52" t="n">
@@ -4130,25 +3574,25 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="102" t="n">
+      <c r="B21" s="92" t="n">
         <v>326</v>
       </c>
       <c r="C21" s="43" t="n">
         <v>256</v>
       </c>
-      <c r="D21" s="103" t="n">
+      <c r="D21" s="93" t="n">
         <v>302</v>
       </c>
-      <c r="E21" s="71" t="n">
+      <c r="E21" s="70" t="n">
         <v>364</v>
       </c>
       <c r="F21" s="54" t="n">
         <v>370</v>
       </c>
-      <c r="G21" s="104" t="n">
+      <c r="G21" s="94" t="n">
         <v>419</v>
       </c>
-      <c r="H21" s="104" t="n">
+      <c r="H21" s="94" t="n">
         <v>419</v>
       </c>
       <c r="I21" s="49" t="n">
@@ -4163,7 +3607,7 @@
       <c r="L21" s="57" t="n">
         <v>433</v>
       </c>
-      <c r="M21" s="105" t="n">
+      <c r="M21" s="95" t="n">
         <v>579</v>
       </c>
       <c r="N21" s="53" t="n">
@@ -4196,49 +3640,49 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="106" t="n">
+      <c r="B22" s="63" t="n">
         <v>328</v>
       </c>
-      <c r="C22" s="107" t="n">
+      <c r="C22" s="96" t="n">
         <v>243</v>
       </c>
-      <c r="D22" s="75" t="n">
+      <c r="D22" s="74" t="n">
         <v>292</v>
       </c>
-      <c r="E22" s="108" t="n">
+      <c r="E22" s="97" t="n">
         <v>356</v>
       </c>
-      <c r="F22" s="97" t="n">
+      <c r="F22" s="89" t="n">
         <v>336</v>
       </c>
-      <c r="G22" s="109" t="n">
+      <c r="G22" s="42" t="n">
         <v>407</v>
       </c>
-      <c r="H22" s="109" t="n">
+      <c r="H22" s="42" t="n">
         <v>407</v>
       </c>
       <c r="I22" s="64" t="n">
         <v>385</v>
       </c>
-      <c r="J22" s="108" t="n">
+      <c r="J22" s="97" t="n">
         <v>357</v>
       </c>
-      <c r="K22" s="81" t="n">
+      <c r="K22" s="42" t="n">
         <v>405</v>
       </c>
-      <c r="L22" s="81" t="n">
+      <c r="L22" s="42" t="n">
         <v>405</v>
       </c>
-      <c r="M22" s="110" t="n">
+      <c r="M22" s="62" t="n">
         <v>555</v>
       </c>
       <c r="N22" s="52" t="n">
         <v>582</v>
       </c>
-      <c r="O22" s="111" t="n">
+      <c r="O22" s="52" t="n">
         <v>588</v>
       </c>
-      <c r="P22" s="111" t="n">
+      <c r="P22" s="52" t="n">
         <v>588</v>
       </c>
       <c r="Q22" s="1"/>
@@ -4262,19 +3706,19 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="112" t="n">
+      <c r="B23" s="93" t="n">
         <v>301</v>
       </c>
-      <c r="C23" s="113" t="n">
+      <c r="C23" s="98" t="n">
         <v>251</v>
       </c>
-      <c r="D23" s="92" t="n">
+      <c r="D23" s="84" t="n">
         <v>283</v>
       </c>
-      <c r="E23" s="80" t="n">
+      <c r="E23" s="76" t="n">
         <v>348</v>
       </c>
-      <c r="F23" s="114" t="n">
+      <c r="F23" s="81" t="n">
         <v>330</v>
       </c>
       <c r="G23" s="64" t="n">
@@ -4286,13 +3730,13 @@
       <c r="I23" s="64" t="n">
         <v>385</v>
       </c>
-      <c r="J23" s="80" t="n">
+      <c r="J23" s="76" t="n">
         <v>347</v>
       </c>
-      <c r="K23" s="115" t="n">
+      <c r="K23" s="68" t="n">
         <v>398</v>
       </c>
-      <c r="L23" s="115" t="n">
+      <c r="L23" s="68" t="n">
         <v>398</v>
       </c>
       <c r="M23" s="48" t="n">
@@ -4301,10 +3745,10 @@
       <c r="N23" s="60" t="n">
         <v>543</v>
       </c>
-      <c r="O23" s="105" t="n">
+      <c r="O23" s="95" t="n">
         <v>579</v>
       </c>
-      <c r="P23" s="105" t="n">
+      <c r="P23" s="95" t="n">
         <v>579</v>
       </c>
       <c r="Q23" s="1"/>
@@ -4328,13 +3772,13 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="79" t="n">
+      <c r="B24" s="31" t="n">
         <v>295</v>
       </c>
-      <c r="C24" s="116" t="n">
+      <c r="C24" s="99" t="n">
         <v>229</v>
       </c>
-      <c r="D24" s="117" t="n">
+      <c r="D24" s="100" t="n">
         <v>255</v>
       </c>
       <c r="E24" s="63" t="n">
@@ -4343,22 +3787,22 @@
       <c r="F24" s="63" t="n">
         <v>324</v>
       </c>
-      <c r="G24" s="94" t="n">
+      <c r="G24" s="86" t="n">
         <v>375</v>
       </c>
-      <c r="H24" s="94" t="n">
+      <c r="H24" s="86" t="n">
         <v>375</v>
       </c>
-      <c r="I24" s="94" t="n">
+      <c r="I24" s="86" t="n">
         <v>376</v>
       </c>
       <c r="J24" s="32" t="n">
         <v>318</v>
       </c>
-      <c r="K24" s="118" t="n">
+      <c r="K24" s="101" t="n">
         <v>344</v>
       </c>
-      <c r="L24" s="118" t="n">
+      <c r="L24" s="101" t="n">
         <v>344</v>
       </c>
       <c r="M24" s="48" t="n">
@@ -4367,10 +3811,10 @@
       <c r="N24" s="60" t="n">
         <v>543</v>
       </c>
-      <c r="O24" s="119" t="n">
+      <c r="O24" s="102" t="n">
         <v>552</v>
       </c>
-      <c r="P24" s="119" t="n">
+      <c r="P24" s="102" t="n">
         <v>552</v>
       </c>
       <c r="Q24" s="1"/>
@@ -4400,7 +3844,7 @@
       <c r="C25" s="25" t="n">
         <v>227</v>
       </c>
-      <c r="D25" s="120" t="n">
+      <c r="D25" s="98" t="n">
         <v>248</v>
       </c>
       <c r="E25" s="32" t="n">
@@ -4409,34 +3853,34 @@
       <c r="F25" s="39" t="n">
         <v>309</v>
       </c>
-      <c r="G25" s="71" t="n">
+      <c r="G25" s="70" t="n">
         <v>366</v>
       </c>
-      <c r="H25" s="71" t="n">
+      <c r="H25" s="70" t="n">
         <v>366</v>
       </c>
-      <c r="I25" s="80" t="n">
+      <c r="I25" s="76" t="n">
         <v>348</v>
       </c>
       <c r="J25" s="39" t="n">
         <v>311</v>
       </c>
-      <c r="K25" s="114" t="n">
+      <c r="K25" s="81" t="n">
         <v>329</v>
       </c>
-      <c r="L25" s="114" t="n">
+      <c r="L25" s="81" t="n">
         <v>329</v>
       </c>
       <c r="M25" s="47" t="n">
         <v>484</v>
       </c>
-      <c r="N25" s="73" t="n">
+      <c r="N25" s="72" t="n">
         <v>515</v>
       </c>
-      <c r="O25" s="76" t="n">
+      <c r="O25" s="65" t="n">
         <v>526</v>
       </c>
-      <c r="P25" s="76" t="n">
+      <c r="P25" s="65" t="n">
         <v>526</v>
       </c>
       <c r="Q25" s="1"/>
@@ -4460,49 +3904,49 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="121" t="n">
+      <c r="B26" s="103" t="n">
         <v>272</v>
       </c>
-      <c r="C26" s="122" t="n">
+      <c r="C26" s="104" t="n">
         <v>216</v>
       </c>
-      <c r="D26" s="98" t="n">
+      <c r="D26" s="90" t="n">
         <v>259</v>
       </c>
-      <c r="E26" s="114" t="n">
+      <c r="E26" s="81" t="n">
         <v>330</v>
       </c>
-      <c r="F26" s="123" t="n">
+      <c r="F26" s="105" t="n">
         <v>305</v>
       </c>
-      <c r="G26" s="71" t="n">
+      <c r="G26" s="70" t="n">
         <v>365</v>
       </c>
-      <c r="H26" s="71" t="n">
+      <c r="H26" s="70" t="n">
         <v>365</v>
       </c>
-      <c r="I26" s="124" t="n">
+      <c r="I26" s="101" t="n">
         <v>341</v>
       </c>
-      <c r="J26" s="92" t="n">
+      <c r="J26" s="84" t="n">
         <v>283</v>
       </c>
-      <c r="K26" s="70" t="n">
+      <c r="K26" s="69" t="n">
         <v>315</v>
       </c>
-      <c r="L26" s="70" t="n">
+      <c r="L26" s="69" t="n">
         <v>315</v>
       </c>
-      <c r="M26" s="125" t="n">
+      <c r="M26" s="59" t="n">
         <v>465</v>
       </c>
-      <c r="N26" s="77" t="n">
+      <c r="N26" s="75" t="n">
         <v>489</v>
       </c>
-      <c r="O26" s="76" t="n">
+      <c r="O26" s="65" t="n">
         <v>531</v>
       </c>
-      <c r="P26" s="76" t="n">
+      <c r="P26" s="65" t="n">
         <v>531</v>
       </c>
       <c r="Q26" s="1"/>
@@ -4526,40 +3970,40 @@
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="126" t="n">
+      <c r="B27" s="38" t="n">
         <v>266</v>
       </c>
       <c r="C27" s="25" t="n">
         <v>225</v>
       </c>
-      <c r="D27" s="113" t="n">
+      <c r="D27" s="98" t="n">
         <v>251</v>
       </c>
       <c r="E27" s="63" t="n">
         <v>324</v>
       </c>
-      <c r="F27" s="112" t="n">
+      <c r="F27" s="93" t="n">
         <v>301</v>
       </c>
-      <c r="G27" s="127" t="n">
+      <c r="G27" s="106" t="n">
         <v>337</v>
       </c>
-      <c r="H27" s="127" t="n">
+      <c r="H27" s="106" t="n">
         <v>337</v>
       </c>
-      <c r="I27" s="79" t="n">
+      <c r="I27" s="31" t="n">
         <v>295</v>
       </c>
-      <c r="J27" s="126" t="n">
+      <c r="J27" s="38" t="n">
         <v>266</v>
       </c>
-      <c r="K27" s="112" t="n">
+      <c r="K27" s="93" t="n">
         <v>301</v>
       </c>
-      <c r="L27" s="112" t="n">
+      <c r="L27" s="93" t="n">
         <v>301</v>
       </c>
-      <c r="M27" s="89" t="n">
+      <c r="M27" s="82" t="n">
         <v>457</v>
       </c>
       <c r="N27" s="47" t="n">
@@ -4592,10 +4036,10 @@
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="98" t="n">
+      <c r="B28" s="90" t="n">
         <v>261</v>
       </c>
-      <c r="C28" s="128" t="n">
+      <c r="C28" s="107" t="n">
         <v>197</v>
       </c>
       <c r="D28" s="26" t="n">
@@ -4616,25 +4060,25 @@
       <c r="I28" s="31" t="n">
         <v>298</v>
       </c>
-      <c r="J28" s="113" t="n">
+      <c r="J28" s="98" t="n">
         <v>251</v>
       </c>
-      <c r="K28" s="129" t="n">
+      <c r="K28" s="103" t="n">
         <v>270</v>
       </c>
-      <c r="L28" s="129" t="n">
+      <c r="L28" s="103" t="n">
         <v>270</v>
       </c>
-      <c r="M28" s="72" t="n">
+      <c r="M28" s="71" t="n">
         <v>440</v>
       </c>
-      <c r="N28" s="89" t="n">
+      <c r="N28" s="82" t="n">
         <v>457</v>
       </c>
-      <c r="O28" s="82" t="n">
+      <c r="O28" s="77" t="n">
         <v>494</v>
       </c>
-      <c r="P28" s="82" t="n">
+      <c r="P28" s="77" t="n">
         <v>494</v>
       </c>
       <c r="Q28" s="1"/>
@@ -4658,28 +4102,28 @@
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="120" t="n">
+      <c r="B29" s="98" t="n">
         <v>248</v>
       </c>
-      <c r="C29" s="130" t="n">
+      <c r="C29" s="108" t="n">
         <v>188</v>
       </c>
-      <c r="D29" s="116" t="n">
+      <c r="D29" s="99" t="n">
         <v>228</v>
       </c>
-      <c r="E29" s="123" t="n">
+      <c r="E29" s="105" t="n">
         <v>305</v>
       </c>
       <c r="F29" s="30" t="n">
         <v>287</v>
       </c>
-      <c r="G29" s="103" t="n">
+      <c r="G29" s="93" t="n">
         <v>302</v>
       </c>
-      <c r="H29" s="103" t="n">
+      <c r="H29" s="93" t="n">
         <v>302</v>
       </c>
-      <c r="I29" s="131" t="n">
+      <c r="I29" s="37" t="n">
         <v>284</v>
       </c>
       <c r="J29" s="26" t="n">
@@ -4691,10 +4135,10 @@
       <c r="L29" s="38" t="n">
         <v>268</v>
       </c>
-      <c r="M29" s="132" t="n">
+      <c r="M29" s="109" t="n">
         <v>423</v>
       </c>
-      <c r="N29" s="133" t="n">
+      <c r="N29" s="59" t="n">
         <v>463</v>
       </c>
       <c r="O29" s="59" t="n">
@@ -4724,40 +4168,40 @@
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="134" t="n">
+      <c r="B30" s="96" t="n">
         <v>244</v>
       </c>
-      <c r="C30" s="130" t="n">
+      <c r="C30" s="108" t="n">
         <v>187</v>
       </c>
-      <c r="D30" s="135" t="n">
+      <c r="D30" s="25" t="n">
         <v>223</v>
       </c>
-      <c r="E30" s="112" t="n">
+      <c r="E30" s="93" t="n">
         <v>301</v>
       </c>
-      <c r="F30" s="131" t="n">
+      <c r="F30" s="37" t="n">
         <v>284</v>
       </c>
-      <c r="G30" s="123" t="n">
+      <c r="G30" s="105" t="n">
         <v>306</v>
       </c>
-      <c r="H30" s="123" t="n">
+      <c r="H30" s="105" t="n">
         <v>306</v>
       </c>
       <c r="I30" s="38" t="n">
         <v>269</v>
       </c>
-      <c r="J30" s="136" t="n">
+      <c r="J30" s="110" t="n">
         <v>203</v>
       </c>
       <c r="K30" s="27" t="n">
         <v>247</v>
       </c>
-      <c r="L30" s="137" t="n">
+      <c r="L30" s="111" t="n">
         <v>247</v>
       </c>
-      <c r="M30" s="96" t="n">
+      <c r="M30" s="88" t="n">
         <v>429</v>
       </c>
       <c r="N30" s="57" t="n">
@@ -4790,49 +4234,49 @@
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="138" t="n">
+      <c r="B31" s="96" t="n">
         <v>241</v>
       </c>
-      <c r="C31" s="139" t="n">
+      <c r="C31" s="23" t="n">
         <v>169</v>
       </c>
-      <c r="D31" s="140" t="n">
+      <c r="D31" s="112" t="n">
         <v>209</v>
       </c>
       <c r="E31" s="37" t="n">
         <v>289</v>
       </c>
-      <c r="F31" s="117" t="n">
+      <c r="F31" s="100" t="n">
         <v>254</v>
       </c>
-      <c r="G31" s="141" t="n">
+      <c r="G31" s="84" t="n">
         <v>280</v>
       </c>
-      <c r="H31" s="141" t="n">
+      <c r="H31" s="84" t="n">
         <v>280</v>
       </c>
       <c r="I31" s="43" t="n">
         <v>256</v>
       </c>
-      <c r="J31" s="142" t="n">
+      <c r="J31" s="113" t="n">
         <v>208</v>
       </c>
-      <c r="K31" s="143" t="n">
+      <c r="K31" s="114" t="n">
         <v>210</v>
       </c>
-      <c r="L31" s="143" t="n">
+      <c r="L31" s="114" t="n">
         <v>210</v>
       </c>
-      <c r="M31" s="69" t="n">
+      <c r="M31" s="68" t="n">
         <v>397</v>
       </c>
       <c r="N31" s="42" t="n">
         <v>410</v>
       </c>
-      <c r="O31" s="86" t="n">
+      <c r="O31" s="80" t="n">
         <v>442</v>
       </c>
-      <c r="P31" s="86" t="n">
+      <c r="P31" s="80" t="n">
         <v>442</v>
       </c>
       <c r="Q31" s="1"/>
@@ -4856,10 +4300,10 @@
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="116" t="n">
+      <c r="B32" s="99" t="n">
         <v>229</v>
       </c>
-      <c r="C32" s="144" t="n">
+      <c r="C32" s="115" t="n">
         <v>180</v>
       </c>
       <c r="D32" s="35" t="n">
@@ -4868,7 +4312,7 @@
       <c r="E32" s="30" t="n">
         <v>287</v>
       </c>
-      <c r="F32" s="117" t="n">
+      <c r="F32" s="100" t="n">
         <v>254</v>
       </c>
       <c r="G32" s="36" t="n">
@@ -4877,28 +4321,28 @@
       <c r="H32" s="36" t="n">
         <v>276</v>
       </c>
-      <c r="I32" s="145" t="n">
+      <c r="I32" s="116" t="n">
         <v>243</v>
       </c>
-      <c r="J32" s="146" t="n">
+      <c r="J32" s="117" t="n">
         <v>176</v>
       </c>
-      <c r="K32" s="147" t="n">
+      <c r="K32" s="118" t="n">
         <v>212</v>
       </c>
-      <c r="L32" s="148" t="n">
+      <c r="L32" s="119" t="n">
         <v>212</v>
       </c>
-      <c r="M32" s="83" t="n">
+      <c r="M32" s="78" t="n">
         <v>374</v>
       </c>
-      <c r="N32" s="109" t="n">
+      <c r="N32" s="42" t="n">
         <v>408</v>
       </c>
-      <c r="O32" s="132" t="n">
+      <c r="O32" s="109" t="n">
         <v>424</v>
       </c>
-      <c r="P32" s="132" t="n">
+      <c r="P32" s="109" t="n">
         <v>424</v>
       </c>
       <c r="Q32" s="1"/>
@@ -4925,25 +4369,25 @@
       <c r="B33" s="25" t="n">
         <v>226</v>
       </c>
-      <c r="C33" s="149" t="n">
+      <c r="C33" s="24" t="n">
         <v>172</v>
       </c>
-      <c r="D33" s="150" t="n">
+      <c r="D33" s="107" t="n">
         <v>200</v>
       </c>
-      <c r="E33" s="131" t="n">
+      <c r="E33" s="37" t="n">
         <v>284</v>
       </c>
-      <c r="F33" s="135" t="n">
+      <c r="F33" s="25" t="n">
         <v>224</v>
       </c>
-      <c r="G33" s="92" t="n">
+      <c r="G33" s="84" t="n">
         <v>282</v>
       </c>
-      <c r="H33" s="92" t="n">
+      <c r="H33" s="84" t="n">
         <v>282</v>
       </c>
-      <c r="I33" s="151" t="n">
+      <c r="I33" s="120" t="n">
         <v>233</v>
       </c>
       <c r="J33" s="24" t="n">
@@ -4961,10 +4405,10 @@
       <c r="N33" s="41" t="n">
         <v>390</v>
       </c>
-      <c r="O33" s="109" t="n">
+      <c r="O33" s="42" t="n">
         <v>407</v>
       </c>
-      <c r="P33" s="109" t="n">
+      <c r="P33" s="42" t="n">
         <v>407</v>
       </c>
       <c r="Q33" s="1"/>
@@ -4994,25 +4438,25 @@
       <c r="C34" s="23" t="n">
         <v>166</v>
       </c>
-      <c r="D34" s="152" t="n">
+      <c r="D34" s="28" t="n">
         <v>196</v>
       </c>
-      <c r="E34" s="92" t="n">
+      <c r="E34" s="84" t="n">
         <v>283</v>
       </c>
       <c r="F34" s="25" t="n">
         <v>226</v>
       </c>
-      <c r="G34" s="98" t="n">
+      <c r="G34" s="90" t="n">
         <v>259</v>
       </c>
-      <c r="H34" s="98" t="n">
+      <c r="H34" s="90" t="n">
         <v>259</v>
       </c>
-      <c r="I34" s="153" t="n">
+      <c r="I34" s="121" t="n">
         <v>221</v>
       </c>
-      <c r="J34" s="154" t="n">
+      <c r="J34" s="122" t="n">
         <v>146</v>
       </c>
       <c r="K34" s="24" t="n">
@@ -5021,16 +4465,16 @@
       <c r="L34" s="24" t="n">
         <v>177</v>
       </c>
-      <c r="M34" s="155" t="n">
+      <c r="M34" s="123" t="n">
         <v>352</v>
       </c>
       <c r="N34" s="54" t="n">
         <v>372</v>
       </c>
-      <c r="O34" s="156" t="n">
+      <c r="O34" s="124" t="n">
         <v>420</v>
       </c>
-      <c r="P34" s="156" t="n">
+      <c r="P34" s="124" t="n">
         <v>420</v>
       </c>
       <c r="Q34" s="1"/>
@@ -5054,49 +4498,49 @@
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="152" t="n">
+      <c r="B35" s="28" t="n">
         <v>195</v>
       </c>
-      <c r="C35" s="157" t="n">
+      <c r="C35" s="125" t="n">
         <v>158</v>
       </c>
       <c r="D35" s="28" t="n">
         <v>193</v>
       </c>
-      <c r="E35" s="141" t="n">
+      <c r="E35" s="84" t="n">
         <v>281</v>
       </c>
-      <c r="F35" s="158" t="n">
+      <c r="F35" s="126" t="n">
         <v>218</v>
       </c>
       <c r="G35" s="43" t="n">
         <v>257</v>
       </c>
-      <c r="H35" s="159" t="n">
+      <c r="H35" s="127" t="n">
         <v>257</v>
       </c>
-      <c r="I35" s="160" t="n">
+      <c r="I35" s="128" t="n">
         <v>203</v>
       </c>
-      <c r="J35" s="154" t="n">
+      <c r="J35" s="122" t="n">
         <v>146</v>
       </c>
-      <c r="K35" s="149" t="n">
+      <c r="K35" s="24" t="n">
         <v>172</v>
       </c>
-      <c r="L35" s="149" t="n">
+      <c r="L35" s="24" t="n">
         <v>172</v>
       </c>
-      <c r="M35" s="161" t="n">
+      <c r="M35" s="129" t="n">
         <v>362</v>
       </c>
-      <c r="N35" s="93" t="n">
+      <c r="N35" s="85" t="n">
         <v>383</v>
       </c>
-      <c r="O35" s="69" t="n">
+      <c r="O35" s="68" t="n">
         <v>396</v>
       </c>
-      <c r="P35" s="69" t="n">
+      <c r="P35" s="68" t="n">
         <v>396</v>
       </c>
       <c r="Q35" s="1"/>
@@ -5120,19 +4564,19 @@
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="130" t="n">
+      <c r="B36" s="108" t="n">
         <v>187</v>
       </c>
       <c r="C36" s="19" t="n">
         <v>153</v>
       </c>
-      <c r="D36" s="162" t="n">
+      <c r="D36" s="130" t="n">
         <v>192</v>
       </c>
-      <c r="E36" s="92" t="n">
+      <c r="E36" s="84" t="n">
         <v>282</v>
       </c>
-      <c r="F36" s="148" t="n">
+      <c r="F36" s="119" t="n">
         <v>211</v>
       </c>
       <c r="G36" s="26" t="n">
@@ -5144,25 +4588,25 @@
       <c r="I36" s="28" t="n">
         <v>194</v>
       </c>
-      <c r="J36" s="163" t="n">
+      <c r="J36" s="131" t="n">
         <v>127</v>
       </c>
-      <c r="K36" s="157" t="n">
+      <c r="K36" s="125" t="n">
         <v>158</v>
       </c>
-      <c r="L36" s="157" t="n">
+      <c r="L36" s="125" t="n">
         <v>158</v>
       </c>
-      <c r="M36" s="118" t="n">
+      <c r="M36" s="101" t="n">
         <v>344</v>
       </c>
       <c r="N36" s="55" t="n">
         <v>359</v>
       </c>
-      <c r="O36" s="69" t="n">
+      <c r="O36" s="68" t="n">
         <v>392</v>
       </c>
-      <c r="P36" s="69" t="n">
+      <c r="P36" s="68" t="n">
         <v>392</v>
       </c>
       <c r="Q36" s="1"/>
@@ -5186,31 +4630,31 @@
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="130" t="n">
+      <c r="B37" s="108" t="n">
         <v>188</v>
       </c>
-      <c r="C37" s="154" t="n">
+      <c r="C37" s="122" t="n">
         <v>147</v>
       </c>
-      <c r="D37" s="164" t="n">
+      <c r="D37" s="125" t="n">
         <v>161</v>
       </c>
-      <c r="E37" s="117" t="n">
+      <c r="E37" s="100" t="n">
         <v>254</v>
       </c>
-      <c r="F37" s="165" t="n">
+      <c r="F37" s="132" t="n">
         <v>213</v>
       </c>
-      <c r="G37" s="134" t="n">
+      <c r="G37" s="96" t="n">
         <v>245</v>
       </c>
-      <c r="H37" s="134" t="n">
+      <c r="H37" s="96" t="n">
         <v>245</v>
       </c>
-      <c r="I37" s="130" t="n">
+      <c r="I37" s="108" t="n">
         <v>187</v>
       </c>
-      <c r="J37" s="166" t="n">
+      <c r="J37" s="133" t="n">
         <v>130</v>
       </c>
       <c r="K37" s="18" t="n">
@@ -5219,10 +4663,10 @@
       <c r="L37" s="18" t="n">
         <v>144</v>
       </c>
-      <c r="M37" s="106" t="n">
+      <c r="M37" s="63" t="n">
         <v>327</v>
       </c>
-      <c r="N37" s="85" t="n">
+      <c r="N37" s="79" t="n">
         <v>354</v>
       </c>
       <c r="O37" s="40" t="n">
@@ -5252,28 +4696,28 @@
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="144" t="n">
+      <c r="B38" s="115" t="n">
         <v>180</v>
       </c>
-      <c r="C38" s="167" t="n">
+      <c r="C38" s="134" t="n">
         <v>162</v>
       </c>
-      <c r="D38" s="164" t="n">
+      <c r="D38" s="125" t="n">
         <v>161</v>
       </c>
       <c r="E38" s="43" t="n">
         <v>256</v>
       </c>
-      <c r="F38" s="158" t="n">
+      <c r="F38" s="126" t="n">
         <v>218</v>
       </c>
-      <c r="G38" s="116" t="n">
+      <c r="G38" s="99" t="n">
         <v>228</v>
       </c>
-      <c r="H38" s="116" t="n">
+      <c r="H38" s="99" t="n">
         <v>228</v>
       </c>
-      <c r="I38" s="144" t="n">
+      <c r="I38" s="115" t="n">
         <v>180</v>
       </c>
       <c r="J38" s="16" t="n">
@@ -5285,10 +4729,10 @@
       <c r="L38" s="17" t="n">
         <v>113</v>
       </c>
-      <c r="M38" s="168" t="n">
+      <c r="M38" s="58" t="n">
         <v>322</v>
       </c>
-      <c r="N38" s="124" t="n">
+      <c r="N38" s="101" t="n">
         <v>341</v>
       </c>
       <c r="O38" s="54" t="n">
@@ -5318,49 +4762,49 @@
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="169" t="n">
+      <c r="B39" s="135" t="n">
         <v>182</v>
       </c>
-      <c r="C39" s="170" t="n">
+      <c r="C39" s="136" t="n">
         <v>148</v>
       </c>
-      <c r="D39" s="171" t="n">
+      <c r="D39" s="137" t="n">
         <v>160</v>
       </c>
-      <c r="E39" s="98" t="n">
+      <c r="E39" s="90" t="n">
         <v>258</v>
       </c>
       <c r="F39" s="28" t="n">
         <v>194</v>
       </c>
-      <c r="G39" s="172" t="n">
+      <c r="G39" s="138" t="n">
         <v>219</v>
       </c>
-      <c r="H39" s="172" t="n">
+      <c r="H39" s="138" t="n">
         <v>219</v>
       </c>
       <c r="I39" s="24" t="n">
         <v>175</v>
       </c>
-      <c r="J39" s="173" t="n">
+      <c r="J39" s="139" t="n">
         <v>89</v>
       </c>
-      <c r="K39" s="174" t="n">
+      <c r="K39" s="22" t="n">
         <v>122</v>
       </c>
-      <c r="L39" s="174" t="n">
+      <c r="L39" s="22" t="n">
         <v>122</v>
       </c>
-      <c r="M39" s="175" t="n">
+      <c r="M39" s="140" t="n">
         <v>308</v>
       </c>
-      <c r="N39" s="114" t="n">
+      <c r="N39" s="81" t="n">
         <v>330</v>
       </c>
       <c r="O39" s="54" t="n">
         <v>370</v>
       </c>
-      <c r="P39" s="176" t="n">
+      <c r="P39" s="141" t="n">
         <v>370</v>
       </c>
       <c r="Q39" s="1"/>
@@ -5384,49 +4828,49 @@
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="177" t="n">
+      <c r="B40" s="142" t="n">
         <v>185</v>
       </c>
-      <c r="C40" s="178" t="n">
+      <c r="C40" s="143" t="n">
         <v>144</v>
       </c>
-      <c r="D40" s="179" t="n">
+      <c r="D40" s="144" t="n">
         <v>151</v>
       </c>
-      <c r="E40" s="113" t="n">
+      <c r="E40" s="98" t="n">
         <v>251</v>
       </c>
-      <c r="F40" s="180" t="n">
+      <c r="F40" s="145" t="n">
         <v>199</v>
       </c>
-      <c r="G40" s="181" t="n">
+      <c r="G40" s="146" t="n">
         <v>213</v>
       </c>
-      <c r="H40" s="181" t="n">
+      <c r="H40" s="146" t="n">
         <v>213</v>
       </c>
-      <c r="I40" s="139" t="n">
+      <c r="I40" s="23" t="n">
         <v>169</v>
       </c>
-      <c r="J40" s="182" t="n">
+      <c r="J40" s="21" t="n">
         <v>93</v>
       </c>
-      <c r="K40" s="183" t="n">
+      <c r="K40" s="16" t="n">
         <v>102</v>
       </c>
-      <c r="L40" s="184" t="n">
+      <c r="L40" s="147" t="n">
         <v>102</v>
       </c>
-      <c r="M40" s="185" t="n">
+      <c r="M40" s="148" t="n">
         <v>296</v>
       </c>
-      <c r="N40" s="186" t="n">
+      <c r="N40" s="149" t="n">
         <v>338</v>
       </c>
-      <c r="O40" s="187" t="n">
+      <c r="O40" s="150" t="n">
         <v>362</v>
       </c>
-      <c r="P40" s="188" t="n">
+      <c r="P40" s="151" t="n">
         <v>362</v>
       </c>
       <c r="Q40" s="1"/>
@@ -5450,19 +4894,19 @@
       <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="189" t="n">
+      <c r="B41" s="152" t="n">
         <v>180</v>
       </c>
-      <c r="C41" s="190" t="n">
+      <c r="C41" s="153" t="n">
         <v>150</v>
       </c>
       <c r="D41" s="19" t="n">
         <v>152</v>
       </c>
-      <c r="E41" s="117" t="n">
+      <c r="E41" s="100" t="n">
         <v>255</v>
       </c>
-      <c r="F41" s="191" t="n">
+      <c r="F41" s="154" t="n">
         <v>196</v>
       </c>
       <c r="G41" s="25" t="n">
@@ -5483,16 +4927,16 @@
       <c r="L41" s="16" t="n">
         <v>103</v>
       </c>
-      <c r="M41" s="192" t="n">
+      <c r="M41" s="155" t="n">
         <v>314</v>
       </c>
-      <c r="N41" s="193" t="n">
+      <c r="N41" s="156" t="n">
         <v>329</v>
       </c>
-      <c r="O41" s="194" t="n">
+      <c r="O41" s="157" t="n">
         <v>348</v>
       </c>
-      <c r="P41" s="80" t="n">
+      <c r="P41" s="76" t="n">
         <v>348</v>
       </c>
       <c r="Q41" s="1"/>
@@ -5513,34 +4957,34 @@
       <c r="AF41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="195" t="n">
+      <c r="A42" s="158" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="196" t="n">
+      <c r="B42" s="159" t="n">
         <v>165</v>
       </c>
-      <c r="C42" s="174" t="n">
+      <c r="C42" s="22" t="n">
         <v>118</v>
       </c>
-      <c r="D42" s="197" t="n">
+      <c r="D42" s="160" t="n">
         <v>155</v>
       </c>
-      <c r="E42" s="198" t="n">
+      <c r="E42" s="161" t="n">
         <v>260</v>
       </c>
-      <c r="F42" s="199" t="n">
+      <c r="F42" s="162" t="n">
         <v>194</v>
       </c>
-      <c r="G42" s="140" t="n">
+      <c r="G42" s="112" t="n">
         <v>210</v>
       </c>
-      <c r="H42" s="140" t="n">
+      <c r="H42" s="112" t="n">
         <v>210</v>
       </c>
-      <c r="I42" s="167" t="n">
+      <c r="I42" s="134" t="n">
         <v>163</v>
       </c>
-      <c r="J42" s="200" t="n">
+      <c r="J42" s="6" t="n">
         <v>58</v>
       </c>
       <c r="K42" s="15" t="n">
@@ -5549,16 +4993,16 @@
       <c r="L42" s="15" t="n">
         <v>86</v>
       </c>
-      <c r="M42" s="201" t="n">
+      <c r="M42" s="163" t="n">
         <v>304</v>
       </c>
-      <c r="N42" s="192" t="n">
+      <c r="N42" s="155" t="n">
         <v>314</v>
       </c>
-      <c r="O42" s="202" t="n">
+      <c r="O42" s="164" t="n">
         <v>353</v>
       </c>
-      <c r="P42" s="85" t="n">
+      <c r="P42" s="79" t="n">
         <v>353</v>
       </c>
       <c r="Q42" s="1"/>
@@ -5582,31 +5026,31 @@
       <c r="A43" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="164" t="n">
+      <c r="B43" s="125" t="n">
         <v>161</v>
       </c>
       <c r="C43" s="17" t="n">
         <v>117</v>
       </c>
-      <c r="D43" s="203" t="n">
+      <c r="D43" s="122" t="n">
         <v>149</v>
       </c>
       <c r="E43" s="43" t="n">
         <v>256</v>
       </c>
-      <c r="F43" s="136" t="n">
+      <c r="F43" s="110" t="n">
         <v>203</v>
       </c>
-      <c r="G43" s="158" t="n">
+      <c r="G43" s="126" t="n">
         <v>217</v>
       </c>
-      <c r="H43" s="158" t="n">
+      <c r="H43" s="126" t="n">
         <v>217</v>
       </c>
       <c r="I43" s="20" t="n">
         <v>134</v>
       </c>
-      <c r="J43" s="200" t="n">
+      <c r="J43" s="6" t="n">
         <v>58</v>
       </c>
       <c r="K43" s="8" t="n">
@@ -5615,16 +5059,16 @@
       <c r="L43" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="M43" s="123" t="n">
+      <c r="M43" s="105" t="n">
         <v>305</v>
       </c>
       <c r="N43" s="32" t="n">
         <v>318</v>
       </c>
-      <c r="O43" s="85" t="n">
+      <c r="O43" s="79" t="n">
         <v>349</v>
       </c>
-      <c r="P43" s="85" t="n">
+      <c r="P43" s="79" t="n">
         <v>349</v>
       </c>
       <c r="Q43" s="1"/>
@@ -5648,7 +5092,7 @@
       <c r="A44" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="139" t="n">
+      <c r="B44" s="23" t="n">
         <v>167</v>
       </c>
       <c r="C44" s="20" t="n">
@@ -5657,7 +5101,7 @@
       <c r="D44" s="18" t="n">
         <v>144</v>
       </c>
-      <c r="E44" s="117" t="n">
+      <c r="E44" s="100" t="n">
         <v>254</v>
       </c>
       <c r="F44" s="28" t="n">
@@ -5672,7 +5116,7 @@
       <c r="I44" s="18" t="n">
         <v>143</v>
       </c>
-      <c r="J44" s="200" t="n">
+      <c r="J44" s="6" t="n">
         <v>57</v>
       </c>
       <c r="K44" s="15" t="n">
@@ -5681,16 +5125,16 @@
       <c r="L44" s="15" t="n">
         <v>84</v>
       </c>
-      <c r="M44" s="84" t="n">
+      <c r="M44" s="74" t="n">
         <v>290</v>
       </c>
-      <c r="N44" s="99" t="n">
+      <c r="N44" s="32" t="n">
         <v>313</v>
       </c>
-      <c r="O44" s="114" t="n">
+      <c r="O44" s="81" t="n">
         <v>329</v>
       </c>
-      <c r="P44" s="114" t="n">
+      <c r="P44" s="81" t="n">
         <v>329</v>
       </c>
       <c r="Q44" s="1"/>
@@ -5720,25 +5164,25 @@
       <c r="C45" s="20" t="n">
         <v>135</v>
       </c>
-      <c r="D45" s="203" t="n">
+      <c r="D45" s="122" t="n">
         <v>148</v>
       </c>
-      <c r="E45" s="98" t="n">
+      <c r="E45" s="90" t="n">
         <v>261</v>
       </c>
-      <c r="F45" s="204" t="n">
+      <c r="F45" s="165" t="n">
         <v>184</v>
       </c>
-      <c r="G45" s="148" t="n">
+      <c r="G45" s="119" t="n">
         <v>211</v>
       </c>
-      <c r="H45" s="148" t="n">
+      <c r="H45" s="119" t="n">
         <v>211</v>
       </c>
       <c r="I45" s="20" t="n">
         <v>133</v>
       </c>
-      <c r="J45" s="200" t="n">
+      <c r="J45" s="6" t="n">
         <v>58</v>
       </c>
       <c r="K45" s="10" t="n">
@@ -5747,16 +5191,16 @@
       <c r="L45" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="M45" s="75" t="n">
+      <c r="M45" s="74" t="n">
         <v>293</v>
       </c>
       <c r="N45" s="39" t="n">
         <v>311</v>
       </c>
-      <c r="O45" s="114" t="n">
+      <c r="O45" s="81" t="n">
         <v>329</v>
       </c>
-      <c r="P45" s="114" t="n">
+      <c r="P45" s="81" t="n">
         <v>329</v>
       </c>
       <c r="Q45" s="1"/>
@@ -5789,19 +5233,19 @@
       <c r="D46" s="18" t="n">
         <v>144</v>
       </c>
-      <c r="E46" s="98" t="n">
+      <c r="E46" s="90" t="n">
         <v>259</v>
       </c>
-      <c r="F46" s="205" t="n">
+      <c r="F46" s="166" t="n">
         <v>185</v>
       </c>
-      <c r="G46" s="162" t="n">
+      <c r="G46" s="130" t="n">
         <v>191</v>
       </c>
-      <c r="H46" s="162" t="n">
+      <c r="H46" s="130" t="n">
         <v>191</v>
       </c>
-      <c r="I46" s="154" t="n">
+      <c r="I46" s="122" t="n">
         <v>146</v>
       </c>
       <c r="J46" s="5" t="n">
@@ -5813,7 +5257,7 @@
       <c r="L46" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="M46" s="112" t="n">
+      <c r="M46" s="93" t="n">
         <v>299</v>
       </c>
       <c r="N46" s="58" t="n">
@@ -5852,31 +5296,31 @@
       <c r="C47" s="22" t="n">
         <v>126</v>
       </c>
-      <c r="D47" s="203" t="n">
+      <c r="D47" s="122" t="n">
         <v>149</v>
       </c>
       <c r="E47" s="38" t="n">
         <v>268</v>
       </c>
-      <c r="F47" s="130" t="n">
+      <c r="F47" s="108" t="n">
         <v>188</v>
       </c>
-      <c r="G47" s="148" t="n">
+      <c r="G47" s="119" t="n">
         <v>211</v>
       </c>
-      <c r="H47" s="148" t="n">
+      <c r="H47" s="119" t="n">
         <v>211</v>
       </c>
-      <c r="I47" s="206" t="n">
+      <c r="I47" s="167" t="n">
         <v>140</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="K47" s="200" t="n">
+      <c r="K47" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="L47" s="200" t="n">
+      <c r="L47" s="6" t="n">
         <v>59</v>
       </c>
       <c r="M47" s="31" t="n">
@@ -5885,10 +5329,10 @@
       <c r="N47" s="58" t="n">
         <v>319</v>
       </c>
-      <c r="O47" s="88" t="n">
+      <c r="O47" s="81" t="n">
         <v>334</v>
       </c>
-      <c r="P47" s="88" t="n">
+      <c r="P47" s="81" t="n">
         <v>334</v>
       </c>
       <c r="Q47" s="1"/>
@@ -5915,22 +5359,22 @@
       <c r="B48" s="24" t="n">
         <v>175</v>
       </c>
-      <c r="C48" s="163" t="n">
+      <c r="C48" s="131" t="n">
         <v>128</v>
       </c>
-      <c r="D48" s="207" t="n">
+      <c r="D48" s="125" t="n">
         <v>157</v>
       </c>
-      <c r="E48" s="208" t="n">
+      <c r="E48" s="168" t="n">
         <v>279</v>
       </c>
-      <c r="F48" s="136" t="n">
+      <c r="F48" s="110" t="n">
         <v>201</v>
       </c>
-      <c r="G48" s="135" t="n">
+      <c r="G48" s="25" t="n">
         <v>223</v>
       </c>
-      <c r="H48" s="135" t="n">
+      <c r="H48" s="25" t="n">
         <v>223</v>
       </c>
       <c r="I48" s="22" t="n">
@@ -5945,7 +5389,7 @@
       <c r="L48" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="M48" s="79" t="n">
+      <c r="M48" s="31" t="n">
         <v>296</v>
       </c>
       <c r="N48" s="39" t="n">
@@ -5981,13 +5425,13 @@
       <c r="B49" s="24" t="n">
         <v>176</v>
       </c>
-      <c r="C49" s="166" t="n">
+      <c r="C49" s="133" t="n">
         <v>130</v>
       </c>
-      <c r="D49" s="154" t="n">
+      <c r="D49" s="122" t="n">
         <v>147</v>
       </c>
-      <c r="E49" s="129" t="n">
+      <c r="E49" s="103" t="n">
         <v>271</v>
       </c>
       <c r="F49" s="35" t="n">
@@ -5999,10 +5443,10 @@
       <c r="H49" s="34" t="n">
         <v>215</v>
       </c>
-      <c r="I49" s="206" t="n">
+      <c r="I49" s="167" t="n">
         <v>141</v>
       </c>
-      <c r="J49" s="209" t="n">
+      <c r="J49" s="3" t="n">
         <v>38</v>
       </c>
       <c r="K49" s="9" t="n">
@@ -6011,16 +5455,16 @@
       <c r="L49" s="9" t="n">
         <v>52</v>
       </c>
-      <c r="M49" s="123" t="n">
+      <c r="M49" s="105" t="n">
         <v>306</v>
       </c>
-      <c r="N49" s="102" t="n">
+      <c r="N49" s="92" t="n">
         <v>326</v>
       </c>
-      <c r="O49" s="85" t="n">
+      <c r="O49" s="79" t="n">
         <v>355</v>
       </c>
-      <c r="P49" s="85" t="n">
+      <c r="P49" s="79" t="n">
         <v>355</v>
       </c>
       <c r="Q49" s="1"/>
@@ -6044,49 +5488,49 @@
       <c r="A50" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="130" t="n">
+      <c r="B50" s="108" t="n">
         <v>188</v>
       </c>
       <c r="C50" s="20" t="n">
         <v>134</v>
       </c>
-      <c r="D50" s="207" t="n">
+      <c r="D50" s="125" t="n">
         <v>156</v>
       </c>
-      <c r="E50" s="131" t="n">
+      <c r="E50" s="37" t="n">
         <v>284</v>
       </c>
-      <c r="F50" s="136" t="n">
+      <c r="F50" s="110" t="n">
         <v>201</v>
       </c>
-      <c r="G50" s="116" t="n">
+      <c r="G50" s="99" t="n">
         <v>230</v>
       </c>
-      <c r="H50" s="116" t="n">
+      <c r="H50" s="99" t="n">
         <v>230</v>
       </c>
-      <c r="I50" s="166" t="n">
+      <c r="I50" s="133" t="n">
         <v>130</v>
       </c>
-      <c r="J50" s="210" t="n">
+      <c r="J50" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="K50" s="211" t="n">
+      <c r="K50" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="L50" s="211" t="n">
+      <c r="L50" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="M50" s="112" t="n">
+      <c r="M50" s="93" t="n">
         <v>299</v>
       </c>
-      <c r="N50" s="212" t="n">
+      <c r="N50" s="81" t="n">
         <v>331</v>
       </c>
-      <c r="O50" s="108" t="n">
+      <c r="O50" s="97" t="n">
         <v>356</v>
       </c>
-      <c r="P50" s="108" t="n">
+      <c r="P50" s="97" t="n">
         <v>356</v>
       </c>
       <c r="Q50" s="1"/>
@@ -6110,19 +5554,19 @@
       <c r="A51" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="149" t="n">
+      <c r="B51" s="24" t="n">
         <v>172</v>
       </c>
-      <c r="C51" s="213" t="n">
+      <c r="C51" s="169" t="n">
         <v>137</v>
       </c>
       <c r="D51" s="23" t="n">
         <v>165</v>
       </c>
-      <c r="E51" s="79" t="n">
+      <c r="E51" s="31" t="n">
         <v>296</v>
       </c>
-      <c r="F51" s="214" t="n">
+      <c r="F51" s="112" t="n">
         <v>208</v>
       </c>
       <c r="G51" s="25" t="n">
@@ -6131,10 +5575,10 @@
       <c r="H51" s="25" t="n">
         <v>226</v>
       </c>
-      <c r="I51" s="203" t="n">
+      <c r="I51" s="122" t="n">
         <v>149</v>
       </c>
-      <c r="J51" s="210" t="n">
+      <c r="J51" s="3" t="n">
         <v>34</v>
       </c>
       <c r="K51" s="8" t="n">
@@ -6143,16 +5587,16 @@
       <c r="L51" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="M51" s="201" t="n">
+      <c r="M51" s="163" t="n">
         <v>303</v>
       </c>
       <c r="N51" s="44" t="n">
         <v>339</v>
       </c>
-      <c r="O51" s="71" t="n">
+      <c r="O51" s="70" t="n">
         <v>366</v>
       </c>
-      <c r="P51" s="71" t="n">
+      <c r="P51" s="70" t="n">
         <v>366</v>
       </c>
       <c r="Q51" s="1"/>
@@ -6176,49 +5620,49 @@
       <c r="A52" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="130" t="n">
+      <c r="B52" s="108" t="n">
         <v>187</v>
       </c>
       <c r="C52" s="20" t="n">
         <v>133</v>
       </c>
-      <c r="D52" s="139" t="n">
+      <c r="D52" s="23" t="n">
         <v>167</v>
       </c>
-      <c r="E52" s="112" t="n">
+      <c r="E52" s="93" t="n">
         <v>301</v>
       </c>
-      <c r="F52" s="122" t="n">
+      <c r="F52" s="104" t="n">
         <v>216</v>
       </c>
-      <c r="G52" s="107" t="n">
+      <c r="G52" s="96" t="n">
         <v>242</v>
       </c>
-      <c r="H52" s="107" t="n">
+      <c r="H52" s="96" t="n">
         <v>242</v>
       </c>
-      <c r="I52" s="203" t="n">
+      <c r="I52" s="122" t="n">
         <v>148</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="K52" s="200" t="n">
+      <c r="K52" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="L52" s="200" t="n">
+      <c r="L52" s="6" t="n">
         <v>58</v>
       </c>
       <c r="M52" s="58" t="n">
         <v>319</v>
       </c>
-      <c r="N52" s="108" t="n">
+      <c r="N52" s="97" t="n">
         <v>358</v>
       </c>
-      <c r="O52" s="215" t="n">
+      <c r="O52" s="170" t="n">
         <v>388</v>
       </c>
-      <c r="P52" s="215" t="n">
+      <c r="P52" s="170" t="n">
         <v>388</v>
       </c>
       <c r="Q52" s="1"/>
@@ -6242,43 +5686,43 @@
       <c r="A53" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="136" t="n">
+      <c r="B53" s="110" t="n">
         <v>201</v>
       </c>
-      <c r="C53" s="157" t="n">
+      <c r="C53" s="125" t="n">
         <v>158</v>
       </c>
-      <c r="D53" s="216" t="n">
+      <c r="D53" s="171" t="n">
         <v>178</v>
       </c>
-      <c r="E53" s="70" t="n">
+      <c r="E53" s="69" t="n">
         <v>315</v>
       </c>
       <c r="F53" s="26" t="n">
         <v>235</v>
       </c>
-      <c r="G53" s="138" t="n">
+      <c r="G53" s="96" t="n">
         <v>240</v>
       </c>
-      <c r="H53" s="138" t="n">
+      <c r="H53" s="96" t="n">
         <v>240</v>
       </c>
-      <c r="I53" s="190" t="n">
+      <c r="I53" s="153" t="n">
         <v>150</v>
       </c>
-      <c r="J53" s="217" t="n">
+      <c r="J53" s="172" t="n">
         <v>46</v>
       </c>
-      <c r="K53" s="218" t="n">
+      <c r="K53" s="173" t="n">
         <v>56</v>
       </c>
-      <c r="L53" s="218" t="n">
+      <c r="L53" s="173" t="n">
         <v>56</v>
       </c>
-      <c r="M53" s="219" t="n">
+      <c r="M53" s="174" t="n">
         <v>346</v>
       </c>
-      <c r="N53" s="100" t="n">
+      <c r="N53" s="91" t="n">
         <v>369</v>
       </c>
       <c r="O53" s="64" t="n">
@@ -6308,25 +5752,25 @@
       <c r="A54" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="150" t="n">
+      <c r="B54" s="107" t="n">
         <v>199</v>
       </c>
       <c r="C54" s="23" t="n">
         <v>164</v>
       </c>
-      <c r="D54" s="167" t="n">
+      <c r="D54" s="134" t="n">
         <v>162</v>
       </c>
-      <c r="E54" s="201" t="n">
+      <c r="E54" s="163" t="n">
         <v>303</v>
       </c>
-      <c r="F54" s="122" t="n">
+      <c r="F54" s="104" t="n">
         <v>216</v>
       </c>
-      <c r="G54" s="98" t="n">
+      <c r="G54" s="90" t="n">
         <v>260</v>
       </c>
-      <c r="H54" s="98" t="n">
+      <c r="H54" s="90" t="n">
         <v>260</v>
       </c>
       <c r="I54" s="23" t="n">
@@ -6335,22 +5779,22 @@
       <c r="J54" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="K54" s="220" t="n">
+      <c r="K54" s="175" t="n">
         <v>75</v>
       </c>
-      <c r="L54" s="220" t="n">
+      <c r="L54" s="175" t="n">
         <v>75</v>
       </c>
-      <c r="M54" s="71" t="n">
+      <c r="M54" s="70" t="n">
         <v>366</v>
       </c>
-      <c r="N54" s="108" t="n">
+      <c r="N54" s="97" t="n">
         <v>356</v>
       </c>
-      <c r="O54" s="93" t="n">
+      <c r="O54" s="85" t="n">
         <v>382</v>
       </c>
-      <c r="P54" s="93" t="n">
+      <c r="P54" s="85" t="n">
         <v>382</v>
       </c>
       <c r="Q54" s="1"/>
@@ -6374,49 +5818,49 @@
       <c r="A55" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="122" t="n">
+      <c r="B55" s="104" t="n">
         <v>216</v>
       </c>
-      <c r="C55" s="149" t="n">
+      <c r="C55" s="24" t="n">
         <v>172</v>
       </c>
       <c r="D55" s="24" t="n">
         <v>176</v>
       </c>
-      <c r="E55" s="168" t="n">
+      <c r="E55" s="58" t="n">
         <v>321</v>
       </c>
       <c r="F55" s="29" t="n">
         <v>237</v>
       </c>
-      <c r="G55" s="221" t="n">
+      <c r="G55" s="43" t="n">
         <v>252</v>
       </c>
-      <c r="H55" s="221" t="n">
+      <c r="H55" s="43" t="n">
         <v>252</v>
       </c>
-      <c r="I55" s="216" t="n">
+      <c r="I55" s="171" t="n">
         <v>178</v>
       </c>
-      <c r="J55" s="210" t="n">
+      <c r="J55" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="K55" s="222" t="n">
+      <c r="K55" s="175" t="n">
         <v>77</v>
       </c>
-      <c r="L55" s="222" t="n">
+      <c r="L55" s="175" t="n">
         <v>77</v>
       </c>
-      <c r="M55" s="94" t="n">
+      <c r="M55" s="86" t="n">
         <v>377</v>
       </c>
-      <c r="N55" s="93" t="n">
+      <c r="N55" s="85" t="n">
         <v>381</v>
       </c>
-      <c r="O55" s="81" t="n">
+      <c r="O55" s="42" t="n">
         <v>401</v>
       </c>
-      <c r="P55" s="81" t="n">
+      <c r="P55" s="42" t="n">
         <v>401</v>
       </c>
       <c r="Q55" s="1"/>
@@ -6443,22 +5887,22 @@
       <c r="B56" s="26" t="n">
         <v>235</v>
       </c>
-      <c r="C56" s="167" t="n">
+      <c r="C56" s="134" t="n">
         <v>162</v>
       </c>
-      <c r="D56" s="162" t="n">
+      <c r="D56" s="130" t="n">
         <v>191</v>
       </c>
       <c r="E56" s="44" t="n">
         <v>339</v>
       </c>
-      <c r="F56" s="138" t="n">
+      <c r="F56" s="96" t="n">
         <v>240</v>
       </c>
-      <c r="G56" s="223" t="n">
+      <c r="G56" s="168" t="n">
         <v>274</v>
       </c>
-      <c r="H56" s="223" t="n">
+      <c r="H56" s="168" t="n">
         <v>274</v>
       </c>
       <c r="I56" s="24" t="n">
@@ -6467,16 +5911,16 @@
       <c r="J56" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="K56" s="224" t="n">
+      <c r="K56" s="175" t="n">
         <v>80</v>
       </c>
-      <c r="L56" s="224" t="n">
+      <c r="L56" s="175" t="n">
         <v>80</v>
       </c>
-      <c r="M56" s="85" t="n">
+      <c r="M56" s="79" t="n">
         <v>354</v>
       </c>
-      <c r="N56" s="115" t="n">
+      <c r="N56" s="68" t="n">
         <v>398</v>
       </c>
       <c r="O56" s="57" t="n">
@@ -6506,49 +5950,49 @@
       <c r="A57" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="122" t="n">
+      <c r="B57" s="104" t="n">
         <v>216</v>
       </c>
-      <c r="C57" s="149" t="n">
+      <c r="C57" s="24" t="n">
         <v>172</v>
       </c>
-      <c r="D57" s="128" t="n">
+      <c r="D57" s="107" t="n">
         <v>197</v>
       </c>
-      <c r="E57" s="85" t="n">
+      <c r="E57" s="79" t="n">
         <v>349</v>
       </c>
-      <c r="F57" s="225" t="n">
+      <c r="F57" s="176" t="n">
         <v>263</v>
       </c>
-      <c r="G57" s="208" t="n">
+      <c r="G57" s="168" t="n">
         <v>278</v>
       </c>
-      <c r="H57" s="208" t="n">
+      <c r="H57" s="168" t="n">
         <v>278</v>
       </c>
-      <c r="I57" s="136" t="n">
+      <c r="I57" s="110" t="n">
         <v>203</v>
       </c>
       <c r="J57" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="K57" s="226" t="n">
+      <c r="K57" s="177" t="n">
         <v>95</v>
       </c>
-      <c r="L57" s="226" t="n">
+      <c r="L57" s="177" t="n">
         <v>95</v>
       </c>
-      <c r="M57" s="115" t="n">
+      <c r="M57" s="68" t="n">
         <v>399</v>
       </c>
-      <c r="N57" s="104" t="n">
+      <c r="N57" s="94" t="n">
         <v>417</v>
       </c>
-      <c r="O57" s="227" t="n">
+      <c r="O57" s="80" t="n">
         <v>445</v>
       </c>
-      <c r="P57" s="227" t="n">
+      <c r="P57" s="80" t="n">
         <v>445</v>
       </c>
       <c r="Q57" s="1"/>
@@ -6575,28 +6019,28 @@
       <c r="B58" s="29" t="n">
         <v>237</v>
       </c>
-      <c r="C58" s="169" t="n">
+      <c r="C58" s="135" t="n">
         <v>182</v>
       </c>
-      <c r="D58" s="165" t="n">
+      <c r="D58" s="132" t="n">
         <v>214</v>
       </c>
       <c r="E58" s="54" t="n">
         <v>370</v>
       </c>
-      <c r="F58" s="98" t="n">
+      <c r="F58" s="90" t="n">
         <v>259</v>
       </c>
-      <c r="G58" s="201" t="n">
+      <c r="G58" s="163" t="n">
         <v>304</v>
       </c>
-      <c r="H58" s="201" t="n">
+      <c r="H58" s="163" t="n">
         <v>304</v>
       </c>
-      <c r="I58" s="136" t="n">
+      <c r="I58" s="110" t="n">
         <v>203</v>
       </c>
-      <c r="J58" s="224" t="n">
+      <c r="J58" s="175" t="n">
         <v>79</v>
       </c>
       <c r="K58" s="15" t="n">
@@ -6608,13 +6052,13 @@
       <c r="M58" s="49" t="n">
         <v>416</v>
       </c>
-      <c r="N58" s="228" t="n">
+      <c r="N58" s="178" t="n">
         <v>449</v>
       </c>
-      <c r="O58" s="90" t="n">
+      <c r="O58" s="83" t="n">
         <v>461</v>
       </c>
-      <c r="P58" s="90" t="n">
+      <c r="P58" s="83" t="n">
         <v>461</v>
       </c>
       <c r="Q58" s="1"/>
@@ -6638,16 +6082,16 @@
       <c r="A59" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="120" t="n">
+      <c r="B59" s="98" t="n">
         <v>249</v>
       </c>
-      <c r="C59" s="169" t="n">
+      <c r="C59" s="135" t="n">
         <v>183</v>
       </c>
-      <c r="D59" s="151" t="n">
+      <c r="D59" s="120" t="n">
         <v>233</v>
       </c>
-      <c r="E59" s="69" t="n">
+      <c r="E59" s="68" t="n">
         <v>392</v>
       </c>
       <c r="F59" s="30" t="n">
@@ -6662,25 +6106,25 @@
       <c r="I59" s="35" t="n">
         <v>204</v>
       </c>
-      <c r="J59" s="224" t="n">
+      <c r="J59" s="175" t="n">
         <v>81</v>
       </c>
-      <c r="K59" s="182" t="n">
+      <c r="K59" s="21" t="n">
         <v>93</v>
       </c>
-      <c r="L59" s="182" t="n">
+      <c r="L59" s="21" t="n">
         <v>93</v>
       </c>
-      <c r="M59" s="95" t="n">
+      <c r="M59" s="87" t="n">
         <v>436</v>
       </c>
       <c r="N59" s="59" t="n">
         <v>472</v>
       </c>
-      <c r="O59" s="82" t="n">
+      <c r="O59" s="77" t="n">
         <v>498</v>
       </c>
-      <c r="P59" s="82" t="n">
+      <c r="P59" s="77" t="n">
         <v>498</v>
       </c>
       <c r="Q59" s="1"/>
@@ -6704,19 +6148,19 @@
       <c r="A60" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="225" t="n">
+      <c r="B60" s="176" t="n">
         <v>263</v>
       </c>
       <c r="C60" s="35" t="n">
         <v>204</v>
       </c>
-      <c r="D60" s="229" t="n">
+      <c r="D60" s="120" t="n">
         <v>232</v>
       </c>
-      <c r="E60" s="69" t="n">
+      <c r="E60" s="68" t="n">
         <v>396</v>
       </c>
-      <c r="F60" s="201" t="n">
+      <c r="F60" s="163" t="n">
         <v>304</v>
       </c>
       <c r="G60" s="44" t="n">
@@ -6743,10 +6187,10 @@
       <c r="N60" s="59" t="n">
         <v>469</v>
       </c>
-      <c r="O60" s="87" t="n">
+      <c r="O60" s="48" t="n">
         <v>509</v>
       </c>
-      <c r="P60" s="87" t="n">
+      <c r="P60" s="48" t="n">
         <v>509</v>
       </c>
       <c r="Q60" s="1"/>
@@ -6773,10 +6217,10 @@
       <c r="B61" s="37" t="n">
         <v>288</v>
       </c>
-      <c r="C61" s="158" t="n">
+      <c r="C61" s="126" t="n">
         <v>218</v>
       </c>
-      <c r="D61" s="134" t="n">
+      <c r="D61" s="96" t="n">
         <v>244</v>
       </c>
       <c r="E61" s="49" t="n">
@@ -6785,28 +6229,28 @@
       <c r="F61" s="63" t="n">
         <v>323</v>
       </c>
-      <c r="G61" s="155" t="n">
+      <c r="G61" s="123" t="n">
         <v>350</v>
       </c>
-      <c r="H61" s="155" t="n">
+      <c r="H61" s="123" t="n">
         <v>350</v>
       </c>
-      <c r="I61" s="107" t="n">
+      <c r="I61" s="96" t="n">
         <v>242</v>
       </c>
-      <c r="J61" s="174" t="n">
+      <c r="J61" s="22" t="n">
         <v>118</v>
       </c>
-      <c r="K61" s="154" t="n">
+      <c r="K61" s="122" t="n">
         <v>146</v>
       </c>
-      <c r="L61" s="154" t="n">
+      <c r="L61" s="122" t="n">
         <v>146</v>
       </c>
       <c r="M61" s="59" t="n">
         <v>473</v>
       </c>
-      <c r="N61" s="82" t="n">
+      <c r="N61" s="77" t="n">
         <v>497</v>
       </c>
       <c r="O61" s="60" t="n">
@@ -6836,25 +6280,25 @@
       <c r="A62" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="123" t="n">
+      <c r="B62" s="105" t="n">
         <v>305</v>
       </c>
-      <c r="C62" s="230" t="n">
+      <c r="C62" s="179" t="n">
         <v>222</v>
       </c>
-      <c r="D62" s="126" t="n">
+      <c r="D62" s="38" t="n">
         <v>266</v>
       </c>
-      <c r="E62" s="65" t="n">
+      <c r="E62" s="57" t="n">
         <v>438</v>
       </c>
-      <c r="F62" s="88" t="n">
+      <c r="F62" s="81" t="n">
         <v>333</v>
       </c>
-      <c r="G62" s="93" t="n">
+      <c r="G62" s="85" t="n">
         <v>382</v>
       </c>
-      <c r="H62" s="93" t="n">
+      <c r="H62" s="85" t="n">
         <v>382</v>
       </c>
       <c r="I62" s="38" t="n">
@@ -6863,22 +6307,22 @@
       <c r="J62" s="17" t="n">
         <v>117</v>
       </c>
-      <c r="K62" s="231" t="n">
+      <c r="K62" s="180" t="n">
         <v>170</v>
       </c>
-      <c r="L62" s="231" t="n">
+      <c r="L62" s="180" t="n">
         <v>170</v>
       </c>
-      <c r="M62" s="77" t="n">
+      <c r="M62" s="75" t="n">
         <v>490</v>
       </c>
-      <c r="N62" s="232" t="n">
+      <c r="N62" s="181" t="n">
         <v>538</v>
       </c>
-      <c r="O62" s="233" t="n">
+      <c r="O62" s="182" t="n">
         <v>576</v>
       </c>
-      <c r="P62" s="233" t="n">
+      <c r="P62" s="182" t="n">
         <v>576</v>
       </c>
       <c r="Q62" s="1"/>
@@ -6908,37 +6352,37 @@
       <c r="C63" s="29" t="n">
         <v>238</v>
       </c>
-      <c r="D63" s="208" t="n">
+      <c r="D63" s="168" t="n">
         <v>279</v>
       </c>
       <c r="E63" s="50" t="n">
         <v>455</v>
       </c>
-      <c r="F63" s="80" t="n">
+      <c r="F63" s="76" t="n">
         <v>347</v>
       </c>
-      <c r="G63" s="215" t="n">
+      <c r="G63" s="170" t="n">
         <v>387</v>
       </c>
-      <c r="H63" s="215" t="n">
+      <c r="H63" s="170" t="n">
         <v>387</v>
       </c>
       <c r="I63" s="31" t="n">
         <v>297</v>
       </c>
-      <c r="J63" s="213" t="n">
+      <c r="J63" s="169" t="n">
         <v>136</v>
       </c>
-      <c r="K63" s="130" t="n">
+      <c r="K63" s="108" t="n">
         <v>187</v>
       </c>
-      <c r="L63" s="130" t="n">
+      <c r="L63" s="108" t="n">
         <v>187</v>
       </c>
-      <c r="M63" s="73" t="n">
+      <c r="M63" s="72" t="n">
         <v>518</v>
       </c>
-      <c r="N63" s="74" t="n">
+      <c r="N63" s="73" t="n">
         <v>571</v>
       </c>
       <c r="O63" s="53" t="n">
@@ -6968,13 +6412,13 @@
       <c r="A64" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="212" t="n">
+      <c r="B64" s="81" t="n">
         <v>332</v>
       </c>
-      <c r="C64" s="117" t="n">
+      <c r="C64" s="100" t="n">
         <v>254</v>
       </c>
-      <c r="D64" s="201" t="n">
+      <c r="D64" s="163" t="n">
         <v>303</v>
       </c>
       <c r="E64" s="47" t="n">
@@ -6983,10 +6427,10 @@
       <c r="F64" s="54" t="n">
         <v>371</v>
       </c>
-      <c r="G64" s="156" t="n">
+      <c r="G64" s="124" t="n">
         <v>422</v>
       </c>
-      <c r="H64" s="156" t="n">
+      <c r="H64" s="124" t="n">
         <v>422</v>
       </c>
       <c r="I64" s="32" t="n">
@@ -6995,13 +6439,13 @@
       <c r="J64" s="23" t="n">
         <v>166</v>
       </c>
-      <c r="K64" s="152" t="n">
+      <c r="K64" s="28" t="n">
         <v>196</v>
       </c>
-      <c r="L64" s="152" t="n">
+      <c r="L64" s="28" t="n">
         <v>196</v>
       </c>
-      <c r="M64" s="78" t="n">
+      <c r="M64" s="61" t="n">
         <v>559</v>
       </c>
       <c r="N64" s="53" t="n">
@@ -7034,31 +6478,31 @@
       <c r="A65" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="155" t="n">
+      <c r="B65" s="123" t="n">
         <v>352</v>
       </c>
-      <c r="C65" s="225" t="n">
+      <c r="C65" s="176" t="n">
         <v>262</v>
       </c>
-      <c r="D65" s="112" t="n">
+      <c r="D65" s="93" t="n">
         <v>300</v>
       </c>
       <c r="E65" s="47" t="n">
         <v>485</v>
       </c>
-      <c r="F65" s="81" t="n">
+      <c r="F65" s="42" t="n">
         <v>405</v>
       </c>
-      <c r="G65" s="72" t="n">
+      <c r="G65" s="71" t="n">
         <v>439</v>
       </c>
-      <c r="H65" s="72" t="n">
+      <c r="H65" s="71" t="n">
         <v>439</v>
       </c>
-      <c r="I65" s="168" t="n">
+      <c r="I65" s="58" t="n">
         <v>322</v>
       </c>
-      <c r="J65" s="234" t="n">
+      <c r="J65" s="130" t="n">
         <v>189</v>
       </c>
       <c r="K65" s="25" t="n">
@@ -7067,7 +6511,7 @@
       <c r="L65" s="25" t="n">
         <v>227</v>
       </c>
-      <c r="M65" s="235" t="n">
+      <c r="M65" s="53" t="n">
         <v>593</v>
       </c>
       <c r="N65" s="53" t="n">
@@ -7103,34 +6547,34 @@
       <c r="B66" s="64" t="n">
         <v>385</v>
       </c>
-      <c r="C66" s="141" t="n">
+      <c r="C66" s="84" t="n">
         <v>280</v>
       </c>
-      <c r="D66" s="106" t="n">
+      <c r="D66" s="63" t="n">
         <v>328</v>
       </c>
-      <c r="E66" s="73" t="n">
+      <c r="E66" s="72" t="n">
         <v>518</v>
       </c>
       <c r="F66" s="49" t="n">
         <v>412</v>
       </c>
-      <c r="G66" s="91" t="n">
+      <c r="G66" s="47" t="n">
         <v>478</v>
       </c>
-      <c r="H66" s="91" t="n">
+      <c r="H66" s="47" t="n">
         <v>478</v>
       </c>
-      <c r="I66" s="97" t="n">
+      <c r="I66" s="89" t="n">
         <v>336</v>
       </c>
       <c r="J66" s="35" t="n">
         <v>204</v>
       </c>
-      <c r="K66" s="113" t="n">
+      <c r="K66" s="98" t="n">
         <v>250</v>
       </c>
-      <c r="L66" s="113" t="n">
+      <c r="L66" s="98" t="n">
         <v>250</v>
       </c>
       <c r="M66" s="53" t="n">
@@ -7166,31 +6610,31 @@
       <c r="A67" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="B67" s="115" t="n">
+      <c r="B67" s="68" t="n">
         <v>399</v>
       </c>
       <c r="C67" s="58" t="n">
         <v>320</v>
       </c>
-      <c r="D67" s="108" t="n">
+      <c r="D67" s="97" t="n">
         <v>356</v>
       </c>
-      <c r="E67" s="119" t="n">
+      <c r="E67" s="102" t="n">
         <v>550</v>
       </c>
-      <c r="F67" s="86" t="n">
+      <c r="F67" s="80" t="n">
         <v>442</v>
       </c>
-      <c r="G67" s="236" t="n">
+      <c r="G67" s="77" t="n">
         <v>500</v>
       </c>
-      <c r="H67" s="236" t="n">
+      <c r="H67" s="77" t="n">
         <v>500</v>
       </c>
-      <c r="I67" s="93" t="n">
+      <c r="I67" s="85" t="n">
         <v>382</v>
       </c>
-      <c r="J67" s="116" t="n">
+      <c r="J67" s="99" t="n">
         <v>230</v>
       </c>
       <c r="K67" s="36" t="n">
@@ -7235,34 +6679,34 @@
       <c r="B68" s="49" t="n">
         <v>414</v>
       </c>
-      <c r="C68" s="124" t="n">
+      <c r="C68" s="101" t="n">
         <v>341</v>
       </c>
-      <c r="D68" s="94" t="n">
+      <c r="D68" s="86" t="n">
         <v>376</v>
       </c>
-      <c r="E68" s="237" t="n">
+      <c r="E68" s="183" t="n">
         <v>575</v>
       </c>
       <c r="F68" s="59" t="n">
         <v>472</v>
       </c>
-      <c r="G68" s="73" t="n">
+      <c r="G68" s="72" t="n">
         <v>514</v>
       </c>
-      <c r="H68" s="73" t="n">
+      <c r="H68" s="72" t="n">
         <v>514</v>
       </c>
       <c r="I68" s="42" t="n">
         <v>410</v>
       </c>
-      <c r="J68" s="98" t="n">
+      <c r="J68" s="90" t="n">
         <v>258</v>
       </c>
-      <c r="K68" s="99" t="n">
+      <c r="K68" s="32" t="n">
         <v>313</v>
       </c>
-      <c r="L68" s="99" t="n">
+      <c r="L68" s="32" t="n">
         <v>313</v>
       </c>
       <c r="M68" s="53" t="n">
@@ -7298,37 +6742,37 @@
       <c r="A69" s="1" t="n">
         <v>67</v>
       </c>
-      <c r="B69" s="72" t="n">
+      <c r="B69" s="71" t="n">
         <v>441</v>
       </c>
-      <c r="C69" s="118" t="n">
+      <c r="C69" s="101" t="n">
         <v>344</v>
       </c>
-      <c r="D69" s="109" t="n">
+      <c r="D69" s="42" t="n">
         <v>407</v>
       </c>
       <c r="E69" s="53" t="n">
         <v>611</v>
       </c>
-      <c r="F69" s="82" t="n">
+      <c r="F69" s="77" t="n">
         <v>493</v>
       </c>
-      <c r="G69" s="78" t="n">
+      <c r="G69" s="61" t="n">
         <v>559</v>
       </c>
-      <c r="H69" s="78" t="n">
+      <c r="H69" s="61" t="n">
         <v>559</v>
       </c>
-      <c r="I69" s="72" t="n">
+      <c r="I69" s="71" t="n">
         <v>441</v>
       </c>
-      <c r="J69" s="129" t="n">
+      <c r="J69" s="103" t="n">
         <v>270</v>
       </c>
-      <c r="K69" s="118" t="n">
+      <c r="K69" s="101" t="n">
         <v>343</v>
       </c>
-      <c r="L69" s="118" t="n">
+      <c r="L69" s="101" t="n">
         <v>343</v>
       </c>
       <c r="M69" s="53" t="n">
@@ -7367,7 +6811,7 @@
       <c r="B70" s="59" t="n">
         <v>470</v>
       </c>
-      <c r="C70" s="100" t="n">
+      <c r="C70" s="91" t="n">
         <v>368</v>
       </c>
       <c r="D70" s="57" t="n">
@@ -7376,25 +6820,25 @@
       <c r="E70" s="53" t="n">
         <v>641</v>
       </c>
-      <c r="F70" s="76" t="n">
+      <c r="F70" s="65" t="n">
         <v>527</v>
       </c>
-      <c r="G70" s="238" t="n">
+      <c r="G70" s="184" t="n">
         <v>568</v>
       </c>
-      <c r="H70" s="238" t="n">
+      <c r="H70" s="184" t="n">
         <v>568</v>
       </c>
-      <c r="I70" s="125" t="n">
+      <c r="I70" s="59" t="n">
         <v>464</v>
       </c>
-      <c r="J70" s="168" t="n">
+      <c r="J70" s="58" t="n">
         <v>322</v>
       </c>
-      <c r="K70" s="100" t="n">
+      <c r="K70" s="91" t="n">
         <v>367</v>
       </c>
-      <c r="L70" s="100" t="n">
+      <c r="L70" s="91" t="n">
         <v>367</v>
       </c>
       <c r="M70" s="53" t="n">
@@ -7430,13 +6874,13 @@
       <c r="A71" s="1" t="n">
         <v>69</v>
       </c>
-      <c r="B71" s="87" t="n">
+      <c r="B71" s="48" t="n">
         <v>510</v>
       </c>
-      <c r="C71" s="69" t="n">
+      <c r="C71" s="68" t="n">
         <v>393</v>
       </c>
-      <c r="D71" s="227" t="n">
+      <c r="D71" s="80" t="n">
         <v>447</v>
       </c>
       <c r="E71" s="53" t="n">
@@ -7451,10 +6895,10 @@
       <c r="H71" s="53" t="n">
         <v>618</v>
       </c>
-      <c r="I71" s="73" t="n">
+      <c r="I71" s="72" t="n">
         <v>519</v>
       </c>
-      <c r="J71" s="80" t="n">
+      <c r="J71" s="76" t="n">
         <v>347</v>
       </c>
       <c r="K71" s="42" t="n">
@@ -7496,7 +6940,7 @@
       <c r="A72" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="B72" s="68" t="n">
+      <c r="B72" s="67" t="n">
         <v>522</v>
       </c>
       <c r="C72" s="42" t="n">
@@ -7508,7 +6952,7 @@
       <c r="E72" s="53" t="n">
         <v>703</v>
       </c>
-      <c r="F72" s="74" t="n">
+      <c r="F72" s="73" t="n">
         <v>570</v>
       </c>
       <c r="G72" s="53" t="n">
@@ -7517,16 +6961,16 @@
       <c r="H72" s="53" t="n">
         <v>649</v>
       </c>
-      <c r="I72" s="232" t="n">
+      <c r="I72" s="181" t="n">
         <v>537</v>
       </c>
-      <c r="J72" s="94" t="n">
+      <c r="J72" s="86" t="n">
         <v>375</v>
       </c>
-      <c r="K72" s="228" t="n">
+      <c r="K72" s="178" t="n">
         <v>448</v>
       </c>
-      <c r="L72" s="228" t="n">
+      <c r="L72" s="178" t="n">
         <v>448</v>
       </c>
       <c r="M72" s="53" t="n">
@@ -7565,10 +7009,10 @@
       <c r="B73" s="61" t="n">
         <v>565</v>
       </c>
-      <c r="C73" s="95" t="n">
+      <c r="C73" s="87" t="n">
         <v>436</v>
       </c>
-      <c r="D73" s="77" t="n">
+      <c r="D73" s="75" t="n">
         <v>491</v>
       </c>
       <c r="E73" s="53" t="n">
@@ -7583,16 +7027,16 @@
       <c r="H73" s="53" t="n">
         <v>703</v>
       </c>
-      <c r="I73" s="233" t="n">
+      <c r="I73" s="182" t="n">
         <v>576</v>
       </c>
-      <c r="J73" s="132" t="n">
+      <c r="J73" s="109" t="n">
         <v>424</v>
       </c>
-      <c r="K73" s="77" t="n">
+      <c r="K73" s="75" t="n">
         <v>489</v>
       </c>
-      <c r="L73" s="77" t="n">
+      <c r="L73" s="75" t="n">
         <v>489</v>
       </c>
       <c r="M73" s="53" t="n">
@@ -7631,10 +7075,10 @@
       <c r="B74" s="53" t="n">
         <v>600</v>
       </c>
-      <c r="C74" s="125" t="n">
+      <c r="C74" s="59" t="n">
         <v>466</v>
       </c>
-      <c r="D74" s="76" t="n">
+      <c r="D74" s="65" t="n">
         <v>530</v>
       </c>
       <c r="E74" s="53" t="n">
@@ -7652,13 +7096,13 @@
       <c r="I74" s="53" t="n">
         <v>637</v>
       </c>
-      <c r="J74" s="89" t="n">
+      <c r="J74" s="82" t="n">
         <v>456</v>
       </c>
-      <c r="K74" s="67" t="n">
+      <c r="K74" s="66" t="n">
         <v>541</v>
       </c>
-      <c r="L74" s="67" t="n">
+      <c r="L74" s="66" t="n">
         <v>541</v>
       </c>
       <c r="M74" s="53" t="n">
@@ -7697,10 +7141,10 @@
       <c r="B75" s="53" t="n">
         <v>637</v>
       </c>
-      <c r="C75" s="239" t="n">
+      <c r="C75" s="75" t="n">
         <v>487</v>
       </c>
-      <c r="D75" s="74" t="n">
+      <c r="D75" s="73" t="n">
         <v>571</v>
       </c>
       <c r="E75" s="53" t="n">
@@ -7763,7 +7207,7 @@
       <c r="B76" s="53" t="n">
         <v>686</v>
       </c>
-      <c r="C76" s="73" t="n">
+      <c r="C76" s="72" t="n">
         <v>519</v>
       </c>
       <c r="D76" s="53" t="n">
@@ -7784,7 +7228,7 @@
       <c r="I76" s="53" t="n">
         <v>720</v>
       </c>
-      <c r="J76" s="119" t="n">
+      <c r="J76" s="102" t="n">
         <v>550</v>
       </c>
       <c r="K76" s="53" t="n">
@@ -7829,7 +7273,7 @@
       <c r="B77" s="53" t="n">
         <v>698</v>
       </c>
-      <c r="C77" s="119" t="n">
+      <c r="C77" s="102" t="n">
         <v>552</v>
       </c>
       <c r="D77" s="53" t="n">
@@ -7850,7 +7294,7 @@
       <c r="I77" s="53" t="n">
         <v>769</v>
       </c>
-      <c r="J77" s="235" t="n">
+      <c r="J77" s="53" t="n">
         <v>590</v>
       </c>
       <c r="K77" s="53" t="n">
@@ -7895,7 +7339,7 @@
       <c r="B78" s="53" t="n">
         <v>750</v>
       </c>
-      <c r="C78" s="105" t="n">
+      <c r="C78" s="95" t="n">
         <v>578</v>
       </c>
       <c r="D78" s="53" t="n">
@@ -8156,49 +7600,49 @@
       <c r="A82" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="B82" s="240" t="n">
+      <c r="B82" s="185" t="n">
         <v>933</v>
       </c>
-      <c r="C82" s="240" t="n">
+      <c r="C82" s="185" t="n">
         <v>716</v>
       </c>
-      <c r="D82" s="240" t="n">
+      <c r="D82" s="185" t="n">
         <v>842</v>
       </c>
-      <c r="E82" s="240" t="n">
+      <c r="E82" s="185" t="n">
         <v>1123</v>
       </c>
-      <c r="F82" s="240" t="n">
+      <c r="F82" s="185" t="n">
         <v>1007</v>
       </c>
-      <c r="G82" s="240" t="n">
+      <c r="G82" s="185" t="n">
         <v>1159</v>
       </c>
-      <c r="H82" s="240" t="n">
+      <c r="H82" s="185" t="n">
         <v>1159</v>
       </c>
-      <c r="I82" s="240" t="n">
+      <c r="I82" s="185" t="n">
         <v>1052</v>
       </c>
-      <c r="J82" s="240" t="n">
+      <c r="J82" s="185" t="n">
         <v>852</v>
       </c>
-      <c r="K82" s="240" t="n">
+      <c r="K82" s="185" t="n">
         <v>970</v>
       </c>
-      <c r="L82" s="240" t="n">
+      <c r="L82" s="185" t="n">
         <v>970</v>
       </c>
-      <c r="M82" s="240" t="n">
+      <c r="M82" s="185" t="n">
         <v>1568</v>
       </c>
-      <c r="N82" s="240" t="n">
+      <c r="N82" s="185" t="n">
         <v>1640</v>
       </c>
-      <c r="O82" s="240" t="n">
+      <c r="O82" s="185" t="n">
         <v>1731</v>
       </c>
-      <c r="P82" s="240" t="n">
+      <c r="P82" s="185" t="n">
         <v>1731</v>
       </c>
       <c r="Q82" s="1"/>
@@ -8222,49 +7666,49 @@
       <c r="A83" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B83" s="241" t="n">
+      <c r="B83" s="186" t="n">
         <v>25909</v>
       </c>
-      <c r="C83" s="241" t="n">
+      <c r="C83" s="186" t="n">
         <v>20052</v>
       </c>
-      <c r="D83" s="241" t="n">
+      <c r="D83" s="186" t="n">
         <v>23321</v>
       </c>
-      <c r="E83" s="241" t="n">
+      <c r="E83" s="186" t="n">
         <v>32649</v>
       </c>
-      <c r="F83" s="241" t="n">
+      <c r="F83" s="186" t="n">
         <v>28513</v>
       </c>
-      <c r="G83" s="241" t="n">
+      <c r="G83" s="186" t="n">
         <v>32463</v>
       </c>
-      <c r="H83" s="241" t="n">
+      <c r="H83" s="186" t="n">
         <v>32463</v>
       </c>
-      <c r="I83" s="241" t="n">
+      <c r="I83" s="186" t="n">
         <v>27903</v>
       </c>
-      <c r="J83" s="241" t="n">
+      <c r="J83" s="186" t="n">
         <v>20790</v>
       </c>
-      <c r="K83" s="241" t="n">
+      <c r="K83" s="186" t="n">
         <v>24023</v>
       </c>
-      <c r="L83" s="241" t="n">
+      <c r="L83" s="186" t="n">
         <v>24023</v>
       </c>
-      <c r="M83" s="241" t="n">
+      <c r="M83" s="186" t="n">
         <v>44238</v>
       </c>
-      <c r="N83" s="241" t="n">
+      <c r="N83" s="186" t="n">
         <v>46786</v>
       </c>
-      <c r="O83" s="241" t="n">
+      <c r="O83" s="186" t="n">
         <v>49436</v>
       </c>
-      <c r="P83" s="241" t="n">
+      <c r="P83" s="186" t="n">
         <v>49436</v>
       </c>
       <c r="Q83" s="1"/>
@@ -8422,11 +7866,11 @@
     </row>
     <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1"/>
-      <c r="B88" s="242"/>
-      <c r="C88" s="243"/>
-      <c r="D88" s="243"/>
-      <c r="E88" s="243"/>
-      <c r="F88" s="243"/>
+      <c r="B88" s="187"/>
+      <c r="C88" s="188"/>
+      <c r="D88" s="188"/>
+      <c r="E88" s="188"/>
+      <c r="F88" s="188"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -8455,12 +7899,12 @@
       <c r="AF88" s="1"/>
     </row>
     <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="195"/>
-      <c r="B89" s="242"/>
-      <c r="C89" s="243"/>
-      <c r="D89" s="243"/>
-      <c r="E89" s="243"/>
-      <c r="F89" s="244"/>
+      <c r="A89" s="158"/>
+      <c r="B89" s="187"/>
+      <c r="C89" s="188"/>
+      <c r="D89" s="188"/>
+      <c r="E89" s="188"/>
+      <c r="F89" s="189"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>

--- a/outputs/54717.xlsx
+++ b/outputs/54717.xlsx
@@ -2893,8 +2893,8 @@
         <v>29</v>
       </c>
       <c r="S10" s="1" t="n">
-        <f aca="false">SUM(INDEX(B:P,S6+2,MATCH(S4,B2:P2,0)):INDEX(B:P,S8+2,MATCH(S4,B2:P2,0)))</f>
-        <v>4304</v>
+        <f aca="false">SUM($A$40:$A$60)</f>
+        <v>1008</v>
       </c>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
